--- a/overseas-ec/財務モデル_越境EC.xlsx
+++ b/overseas-ec/財務モデル_越境EC.xlsx
@@ -12,8 +12,9 @@
     <sheet name="前提" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="単位経済性" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="月次PL" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="感度分析" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="販売台帳" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Lean版" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="感度分析" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="販売台帳" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="289">
   <si>
     <t xml:space="preserve">越境EC事業 財務モデル</t>
   </si>
@@ -168,16 +169,208 @@
     <t xml:space="preserve">自社の実績が出たら、必ず実測値に置き換えてください。推定値のまま意思決定をしないこと。</t>
   </si>
   <si>
-    <t xml:space="preserve">税務判断ではありません</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ Lean</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">版について</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">消費税還付・輸出免税の適用可否は、必ず税理士に確認してください。</t>
   </si>
   <si>
-    <t xml:space="preserve">制度変更に注意</t>
-  </si>
-  <si>
-    <t xml:space="preserve">米国のde minimis廃止・EUの関税改正により、関税前提は変動します。四半期ごとに見直してください。</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Lean</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">版」シート</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">初期投資</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円・個人事業主・兼業を前提にした実証プラン。初年度はこちらを使います。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「前提」「月次</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PL</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」シート</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">法人設立・初期投資</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">400</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円のフル版。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Lean</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">版で実証が済んでから使います。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「単位経済性」シート</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">両方に共通。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">商品あたりの損益で、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Lean</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">版の損益分岐もここから連動します。</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">前提条件</t>
@@ -1375,6 +1568,1136 @@
   </si>
   <si>
     <t xml:space="preserve">黒字転換月</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Lean</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">版：初年度は実証に徹する（初期投資</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">60</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個人事業主・自宅・兼業を前提に、損益分岐点を月商</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円まで下げた構成です。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">青字のセルを書き換えてください。特に </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B16</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（生活費）は、専業にするなら必ず入れてください。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Lean</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">版 初期費用 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(JPY)</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">開業届・青色申告承認申請</t>
+  </si>
+  <si>
+    <t xml:space="preserve">税務署に出すだけ。費用ゼロ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">古物商許可</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中古を扱うなら必須。約</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日かかるので最初に申請</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15SKU</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1SKU</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">あたり</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円で分散する</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">撮影・梱包資材</t>
+  </si>
+  <si>
+    <t xml:space="preserve">照明と背景紙。カメラはスマホで十分</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">保険（年払）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">削らない。米国の訴訟リスクを移転する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">会計ソフト（年額）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">個人向けプラン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">予備費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フル版（前提シート）の初期費用と比較してください</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Lean</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">版 月次固定費 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(JPY)</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">生活費・自分への報酬</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">兼業なら</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。専業なら</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円を入れる（損益分岐が</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍変わる）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自宅の一室。月</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件程度なら数畳で足りる</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">税理士（決算スポットの月割）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ 12</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。顧問契約はしない</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">会計ソフトのみ。</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Amazon</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">大口出品は契約しない</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">保険（年払の月割）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PL</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">保険 年</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ 12</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「単位経済性」シートから連動</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">損益分岐 月商 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(JPY)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件あたり工数（分）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">習熟すると</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分程度まで下がる</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">必要 月間作業時間</t>
+  </si>
+  <si>
+    <t xml:space="preserve">兼業で回せるかの判断材料</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【生活費シナリオ別の損益分岐】</t>
+  </si>
+  <si>
+    <t xml:space="preserve">生活費（月）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月次固定費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">損益分岐 月商</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">専業（生活費を事業から取る）にすると損益分岐が</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍以上になります。実証期間中は兼業を推奨します。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ヶ月 実証計画】</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月商 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(JPY)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">貢献利益 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(JPY)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">固定費 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(JPY)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">営業損益 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(JPY)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">累計営業損益 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(JPY)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">作業時間</t>
+  </si>
+  <si>
+    <t xml:space="preserve">開業届・許認可・仕入準備</t>
+  </si>
+  <si>
+    <t xml:space="preserve">収支トントン</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Day 90 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">判定</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Day 365 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">判定</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Day 365 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">判定】</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">初期投資の回収状況</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月商</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">最大損失（撤退時の目安）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">初期費用から、在庫を</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">割で処分して回収できる額を差し引いた金額</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Lean</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">版の最大の価値は、失敗したときの損失がこの水準に限定されることです。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">損失が限定されているからこそ、撤退の判断を冷静に下せます。</t>
   </si>
   <si>
     <t xml:space="preserve">感度分析：実質貢献利益率</t>
@@ -1566,15 +2889,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="168" formatCode="\¥#,##0;&quot;(¥&quot;#,##0\);\-"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="\¥#,##0;&quot;(¥&quot;#,##0\);\-"/>
+    <numFmt numFmtId="171" formatCode="0.0%;\(0.0%\);\-"/>
+    <numFmt numFmtId="172" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="173" formatCode="#,##0\h"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1661,6 +2988,34 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
@@ -1681,13 +3036,6 @@
       <color rgb="FF595959"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1735,7 +3083,8 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
     </font>
@@ -1749,8 +3098,8 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FFC00000"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
     </font>
@@ -1858,7 +3207,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="96">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1903,6 +3252,22 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1915,35 +3280,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1955,7 +3320,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1963,15 +3328,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2003,7 +3368,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2011,7 +3376,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2019,11 +3384,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2039,11 +3404,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2067,11 +3432,131 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2079,11 +3564,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2091,15 +3576,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2382,7 +3867,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C22"/>
+  <dimension ref="B2:C24"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
@@ -2499,7 +3984,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C21" s="6" t="s">
@@ -2507,11 +3992,27 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="13" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2540,392 +4041,392 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="A4" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="14" t="n">
+      <c r="A5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="18" t="n">
         <v>150</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="15" t="n">
+      <c r="A6" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
+      <c r="A8" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="16" t="n">
+      <c r="A9" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="20" t="n">
         <v>120</v>
       </c>
-      <c r="C9" s="17" t="s">
-        <v>38</v>
+      <c r="C9" s="21" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="18" t="n">
+      <c r="A10" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="22" t="n">
         <v>6000</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="15" t="n">
+      <c r="A11" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="19" t="n">
         <v>0.15</v>
       </c>
-      <c r="C11" s="17" t="s">
-        <v>42</v>
+      <c r="C11" s="21" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="19" t="n">
+      <c r="A12" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="23" t="n">
         <v>6.5</v>
       </c>
-      <c r="C12" s="17" t="s">
-        <v>44</v>
+      <c r="C12" s="21" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="20" t="n">
+      <c r="A13" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="24" t="n">
         <v>0.12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="19" t="n">
+      <c r="A14" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="23" t="n">
         <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="20" t="n">
+      <c r="A15" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="24" t="n">
         <v>0.1</v>
       </c>
-      <c r="C15" s="17" t="s">
-        <v>50</v>
+      <c r="C15" s="21" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="15" t="n">
+      <c r="A16" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="19" t="n">
         <v>0.015</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" s="15" t="n">
+      <c r="A17" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="19" t="n">
         <v>0.04</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
+      <c r="A19" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20" s="21" t="n">
+      <c r="A20" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="25" t="n">
         <v>300000</v>
       </c>
       <c r="C20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" s="21" t="n">
+      <c r="A21" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="25" t="n">
         <v>50000</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="21" t="n">
+      <c r="A22" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="25" t="n">
         <v>30000</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B23" s="21" t="n">
+      <c r="A23" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="25" t="n">
         <v>20000</v>
       </c>
       <c r="C23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B24" s="21" t="n">
+      <c r="A24" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="25" t="n">
         <v>25000</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" s="22" t="n">
+        <v>68</v>
+      </c>
+      <c r="B25" s="26" t="n">
         <f aca="false">SUM(B20:B24)</f>
         <v>425000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
+      <c r="A27" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" s="21" t="n">
+      <c r="A28" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="25" t="n">
         <v>60000</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="B29" s="21" t="n">
+      <c r="A29" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="25" t="n">
         <v>20000</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B30" s="21" t="n">
+      <c r="A30" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" s="25" t="n">
         <v>20000</v>
       </c>
       <c r="C30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B31" s="18" t="n">
+      <c r="A31" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" s="22" t="n">
         <v>2000000</v>
       </c>
-      <c r="C31" s="17" t="s">
-        <v>72</v>
+      <c r="C31" s="21" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" s="21" t="n">
+      <c r="A32" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="25" t="n">
         <v>300000</v>
       </c>
       <c r="C32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" s="21" t="n">
+      <c r="A33" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="25" t="n">
         <v>50000</v>
       </c>
       <c r="C33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B34" s="21" t="n">
+      <c r="A34" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="25" t="n">
         <v>50000</v>
       </c>
       <c r="C34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B35" s="21" t="n">
+      <c r="A35" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="25" t="n">
         <v>1500000</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B36" s="22" t="n">
+        <v>82</v>
+      </c>
+      <c r="B36" s="26" t="n">
         <f aca="false">SUM(B28:B35)</f>
         <v>4000000</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
+      <c r="A38" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B39" s="21" t="n">
+      <c r="A39" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" s="25" t="n">
         <v>4000000</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B40" s="23" t="n">
+        <v>86</v>
+      </c>
+      <c r="B40" s="27" t="n">
         <f aca="false">B39-B36</f>
         <v>0</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
+      <c r="A42" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B43" s="24" t="n">
+      <c r="A43" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B43" s="28" t="n">
         <v>60</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="B44" s="24" t="n">
+      <c r="A44" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" s="28" t="n">
         <v>14</v>
       </c>
-      <c r="C44" s="17" t="s">
-        <v>88</v>
+      <c r="C44" s="21" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="B45" s="24" t="n">
+      <c r="A45" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B45" s="28" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B46" s="25" t="n">
+        <v>95</v>
+      </c>
+      <c r="B46" s="29" t="n">
         <f aca="false">B43+B44-B45</f>
         <v>74</v>
       </c>
-      <c r="C46" s="17" t="s">
-        <v>92</v>
+      <c r="C46" s="21" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2954,281 +4455,281 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" s="26" t="s">
+      <c r="A4" s="30" t="s">
         <v>99</v>
       </c>
+      <c r="B4" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B5" s="28" t="n">
+      <c r="A5" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="32" t="n">
         <f aca="false">前提!$B$9</f>
         <v>120</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="33" t="n">
         <f aca="false">B5*前提!$B$5</f>
         <v>18000</v>
       </c>
-      <c r="D5" s="30" t="n">
+      <c r="D5" s="34" t="n">
         <f aca="false">B5/$B$5</f>
         <v>1</v>
       </c>
-      <c r="E5" s="17" t="s">
-        <v>101</v>
+      <c r="E5" s="21" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B6" s="28" t="n">
+      <c r="A6" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="32" t="n">
         <f aca="false">-前提!$B$10/前提!$B$5</f>
         <v>-40</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="33" t="n">
         <f aca="false">B6*前提!$B$5</f>
         <v>-6000</v>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="34" t="n">
         <f aca="false">B6/$B$5</f>
         <v>-0.333333333333333</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B7" s="28" t="n">
+      <c r="A7" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="32" t="n">
         <f aca="false">-$B$5*前提!$B$11</f>
         <v>-18</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="33" t="n">
         <f aca="false">B7*前提!$B$5</f>
         <v>-2700</v>
       </c>
-      <c r="D7" s="30" t="n">
+      <c r="D7" s="34" t="n">
         <f aca="false">B7/$B$5</f>
         <v>-0.15</v>
       </c>
-      <c r="E7" s="17" t="s">
-        <v>42</v>
+      <c r="E7" s="21" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="B8" s="28" t="n">
+      <c r="A8" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="32" t="n">
         <f aca="false">-前提!$B$12</f>
         <v>-6.5</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="33" t="n">
         <f aca="false">B8*前提!$B$5</f>
         <v>-975</v>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="34" t="n">
         <f aca="false">B8/$B$5</f>
         <v>-0.0541666666666667</v>
       </c>
-      <c r="E8" s="17" t="s">
-        <v>106</v>
+      <c r="E8" s="21" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B9" s="28" t="n">
+      <c r="A9" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="32" t="n">
         <f aca="false">-$B$5*前提!$B$13</f>
         <v>-14.4</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="33" t="n">
         <f aca="false">B9*前提!$B$5</f>
         <v>-2160</v>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="34" t="n">
         <f aca="false">B9/$B$5</f>
         <v>-0.12</v>
       </c>
-      <c r="E9" s="17" t="s">
-        <v>108</v>
+      <c r="E9" s="21" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="B10" s="28" t="n">
+      <c r="A10" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B10" s="32" t="n">
         <f aca="false">-前提!$B$14</f>
         <v>-9</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="33" t="n">
         <f aca="false">B10*前提!$B$5</f>
         <v>-1350</v>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="34" t="n">
         <f aca="false">B10/$B$5</f>
         <v>-0.075</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B11" s="28" t="n">
+      <c r="A11" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="32" t="n">
         <f aca="false">-$B$5*前提!$B$15</f>
         <v>-12</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="33" t="n">
         <f aca="false">B11*前提!$B$5</f>
         <v>-1800</v>
       </c>
-      <c r="D11" s="30" t="n">
+      <c r="D11" s="34" t="n">
         <f aca="false">B11/$B$5</f>
         <v>-0.1</v>
       </c>
-      <c r="E11" s="17" t="s">
-        <v>111</v>
+      <c r="E11" s="21" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="B12" s="28" t="n">
+      <c r="A12" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="32" t="n">
         <f aca="false">-$B$5*前提!$B$16</f>
         <v>-1.8</v>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="33" t="n">
         <f aca="false">B12*前提!$B$5</f>
         <v>-270</v>
       </c>
-      <c r="D12" s="30" t="n">
+      <c r="D12" s="34" t="n">
         <f aca="false">B12/$B$5</f>
         <v>-0.015</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B13" s="28" t="n">
+      <c r="A13" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="32" t="n">
         <f aca="false">-$B$5*前提!$B$17</f>
         <v>-4.8</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="33" t="n">
         <f aca="false">B13*前提!$B$5</f>
         <v>-720</v>
       </c>
-      <c r="D13" s="30" t="n">
+      <c r="D13" s="34" t="n">
         <f aca="false">B13/$B$5</f>
         <v>-0.04</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B14" s="31" t="n">
+        <v>118</v>
+      </c>
+      <c r="B14" s="35" t="n">
         <f aca="false">SUM(B5:B13)</f>
         <v>13.5</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="26" t="n">
         <f aca="false">B14*前提!$B$5</f>
         <v>2025</v>
       </c>
-      <c r="D14" s="32" t="n">
+      <c r="D14" s="36" t="n">
         <f aca="false">B14/$B$5</f>
         <v>0.1125</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="B15" s="28" t="n">
+      <c r="A15" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" s="32" t="n">
         <f aca="false">前提!$B$10*前提!$B$6/前提!$B$5</f>
         <v>4</v>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="33" t="n">
         <f aca="false">B15*前提!$B$5</f>
         <v>600</v>
       </c>
-      <c r="D15" s="30" t="n">
+      <c r="D15" s="34" t="n">
         <f aca="false">B15/$B$5</f>
         <v>0.0333333333333333</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B16" s="33" t="n">
+        <v>122</v>
+      </c>
+      <c r="B16" s="37" t="n">
         <f aca="false">B14+B15</f>
         <v>17.5</v>
       </c>
-      <c r="C16" s="34" t="n">
+      <c r="C16" s="38" t="n">
         <f aca="false">B16*前提!$B$5</f>
         <v>2625</v>
       </c>
-      <c r="D16" s="35" t="n">
+      <c r="D16" s="39" t="n">
         <f aca="false">B16/$B$5</f>
         <v>0.145833333333333</v>
       </c>
-      <c r="E16" s="36" t="s">
-        <v>119</v>
+      <c r="E16" s="40" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B19" s="30" t="n">
+      <c r="A19" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19" s="34" t="n">
         <f aca="false">B16/$B$5</f>
         <v>0.145833333333333</v>
       </c>
@@ -3238,10 +4739,10 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" s="30" t="n">
+      <c r="A20" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="34" t="n">
         <f aca="false">-B6/$B$5</f>
         <v>0.333333333333333</v>
       </c>
@@ -3251,10 +4752,10 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="B21" s="37" t="n">
+      <c r="A21" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" s="41" t="n">
         <f aca="false">B16</f>
         <v>17.5</v>
       </c>
@@ -3265,77 +4766,77 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="B24" s="38" t="n">
+      <c r="A24" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="B24" s="42" t="n">
         <f aca="false">前提!$B$25</f>
         <v>425000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B25" s="22" t="n">
+        <v>130</v>
+      </c>
+      <c r="B25" s="26" t="n">
         <f aca="false">IF(B19&lt;=0,"—",B24/B19)</f>
         <v>2914285.71428571</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B26" s="25" t="n">
+        <v>131</v>
+      </c>
+      <c r="B26" s="29" t="n">
         <f aca="false">IF(OR(B19&lt;=0,C5=0),"—",B25/C5)</f>
         <v>161.904761904762</v>
       </c>
-      <c r="E26" s="17" t="s">
-        <v>128</v>
+      <c r="E26" s="21" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="B27" s="39" t="n">
+      <c r="A27" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="B27" s="43" t="n">
         <f aca="false">IF(B26="—","—",B26/22)</f>
         <v>7.35930735930736</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B30" s="21" t="n">
+      <c r="A30" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="B30" s="25" t="n">
         <v>5500000</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B31" s="22" t="n">
+        <v>138</v>
+      </c>
+      <c r="B31" s="26" t="n">
         <f aca="false">B30*(前提!$B$46/30)*B20</f>
         <v>4522222.22222222</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -3363,853 +4864,853 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="40" t="s">
-        <v>136</v>
+      <c r="A1" s="44" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="41" t="s">
-        <v>138</v>
-      </c>
-      <c r="B4" s="41" t="s">
-        <v>139</v>
-      </c>
-      <c r="C4" s="41" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" s="41" t="s">
-        <v>140</v>
-      </c>
-      <c r="E4" s="41" t="s">
-        <v>141</v>
-      </c>
-      <c r="F4" s="41" t="s">
+      <c r="A4" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="G4" s="41" t="s">
+      <c r="B4" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="H4" s="41" t="s">
+      <c r="C4" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="45" t="s">
         <v>144</v>
       </c>
-      <c r="I4" s="41" t="s">
-        <v>99</v>
+      <c r="E4" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="F4" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="H4" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="45" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="21" t="n">
+      <c r="A5" s="46" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="33" t="n">
         <f aca="false">B5*C5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E5" s="25" t="n">
         <v>425000</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="33" t="n">
         <f aca="false">D5-E5</f>
         <v>-425000</v>
       </c>
-      <c r="G5" s="29" t="n">
+      <c r="G5" s="33" t="n">
         <f aca="false">F5</f>
         <v>-425000</v>
       </c>
-      <c r="H5" s="43" t="n">
+      <c r="H5" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B5/単位経済性!$C$5)</f>
         <v>0</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="42" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="21" t="n">
+      <c r="A6" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" s="25" t="n">
         <v>300000</v>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="19" t="n">
         <v>0.08</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="33" t="n">
         <f aca="false">B6*C6</f>
         <v>24000</v>
       </c>
-      <c r="E6" s="21" t="n">
+      <c r="E6" s="25" t="n">
         <v>425000</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="33" t="n">
         <f aca="false">D6-E6</f>
         <v>-401000</v>
       </c>
-      <c r="G6" s="29" t="n">
+      <c r="G6" s="33" t="n">
         <f aca="false">G5+F6</f>
         <v>-826000</v>
       </c>
-      <c r="H6" s="43" t="n">
+      <c r="H6" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B6/単位経済性!$C$5)</f>
         <v>16.6666666666667</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="B7" s="21" t="n">
+      <c r="A7" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7" s="25" t="n">
         <v>600000</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="19" t="n">
         <v>0.1</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="33" t="n">
         <f aca="false">B7*C7</f>
         <v>60000</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="25" t="n">
         <v>425000</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="33" t="n">
         <f aca="false">D7-E7</f>
         <v>-365000</v>
       </c>
-      <c r="G7" s="29" t="n">
+      <c r="G7" s="33" t="n">
         <f aca="false">G6+F7</f>
         <v>-1191000</v>
       </c>
-      <c r="H7" s="43" t="n">
+      <c r="H7" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B7/単位経済性!$C$5)</f>
         <v>33.3333333333333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="42" t="s">
-        <v>150</v>
-      </c>
-      <c r="B8" s="21" t="n">
+      <c r="A8" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8" s="25" t="n">
         <v>1000000</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="19" t="n">
         <v>0.12</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="33" t="n">
         <f aca="false">B8*C8</f>
         <v>120000</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="25" t="n">
         <v>425000</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="33" t="n">
         <f aca="false">D8-E8</f>
         <v>-305000</v>
       </c>
-      <c r="G8" s="29" t="n">
+      <c r="G8" s="33" t="n">
         <f aca="false">G7+F8</f>
         <v>-1496000</v>
       </c>
-      <c r="H8" s="43" t="n">
+      <c r="H8" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B8/単位経済性!$C$5)</f>
         <v>55.5555555555556</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="42" t="s">
-        <v>151</v>
-      </c>
-      <c r="B9" s="21" t="n">
+      <c r="A9" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="B9" s="25" t="n">
         <v>1400000</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="19" t="n">
         <v>0.13</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="33" t="n">
         <f aca="false">B9*C9</f>
         <v>182000</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="25" t="n">
         <v>425000</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="33" t="n">
         <f aca="false">D9-E9</f>
         <v>-243000</v>
       </c>
-      <c r="G9" s="29" t="n">
+      <c r="G9" s="33" t="n">
         <f aca="false">G8+F9</f>
         <v>-1739000</v>
       </c>
-      <c r="H9" s="43" t="n">
+      <c r="H9" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B9/単位経済性!$C$5)</f>
         <v>77.7777777777778</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="42" t="s">
-        <v>152</v>
-      </c>
-      <c r="B10" s="21" t="n">
+      <c r="A10" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="B10" s="25" t="n">
         <v>1800000</v>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="19" t="n">
         <v>0.14</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="33" t="n">
         <f aca="false">B10*C10</f>
         <v>252000</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="25" t="n">
         <v>425000</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="33" t="n">
         <f aca="false">D10-E10</f>
         <v>-173000</v>
       </c>
-      <c r="G10" s="29" t="n">
+      <c r="G10" s="33" t="n">
         <f aca="false">G9+F10</f>
         <v>-1912000</v>
       </c>
-      <c r="H10" s="43" t="n">
+      <c r="H10" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B10/単位経済性!$C$5)</f>
         <v>100</v>
       </c>
-      <c r="I10" s="17" t="s">
-        <v>153</v>
+      <c r="I10" s="21" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="42" t="s">
-        <v>154</v>
-      </c>
-      <c r="B11" s="21" t="n">
+      <c r="A11" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="B11" s="25" t="n">
         <v>2300000</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="19" t="n">
         <v>0.15</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="33" t="n">
         <f aca="false">B11*C11</f>
         <v>345000</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="25" t="n">
         <v>425000</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="33" t="n">
         <f aca="false">D11-E11</f>
         <v>-80000</v>
       </c>
-      <c r="G11" s="29" t="n">
+      <c r="G11" s="33" t="n">
         <f aca="false">G10+F11</f>
         <v>-1992000</v>
       </c>
-      <c r="H11" s="43" t="n">
+      <c r="H11" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B11/単位経済性!$C$5)</f>
         <v>127.777777777778</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="42" t="s">
-        <v>155</v>
-      </c>
-      <c r="B12" s="21" t="n">
+      <c r="A12" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="B12" s="25" t="n">
         <v>2800000</v>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="19" t="n">
         <v>0.16</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="33" t="n">
         <f aca="false">B12*C12</f>
         <v>448000</v>
       </c>
-      <c r="E12" s="21" t="n">
+      <c r="E12" s="25" t="n">
         <v>450000</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="33" t="n">
         <f aca="false">D12-E12</f>
         <v>-2000</v>
       </c>
-      <c r="G12" s="29" t="n">
+      <c r="G12" s="33" t="n">
         <f aca="false">G11+F12</f>
         <v>-1994000</v>
       </c>
-      <c r="H12" s="43" t="n">
+      <c r="H12" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B12/単位経済性!$C$5)</f>
         <v>155.555555555556</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="B13" s="21" t="n">
+      <c r="A13" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="B13" s="25" t="n">
         <v>3300000</v>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="19" t="n">
         <v>0.16</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="33" t="n">
         <f aca="false">B13*C13</f>
         <v>528000</v>
       </c>
-      <c r="E13" s="21" t="n">
+      <c r="E13" s="25" t="n">
         <v>450000</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="33" t="n">
         <f aca="false">D13-E13</f>
         <v>78000</v>
       </c>
-      <c r="G13" s="29" t="n">
+      <c r="G13" s="33" t="n">
         <f aca="false">G12+F13</f>
         <v>-1916000</v>
       </c>
-      <c r="H13" s="43" t="n">
+      <c r="H13" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B13/単位経済性!$C$5)</f>
         <v>183.333333333333</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="42" t="s">
-        <v>158</v>
-      </c>
-      <c r="B14" s="21" t="n">
+      <c r="A14" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="B14" s="25" t="n">
         <v>4000000</v>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="19" t="n">
         <v>0.17</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="33" t="n">
         <f aca="false">B14*C14</f>
         <v>680000</v>
       </c>
-      <c r="E14" s="21" t="n">
+      <c r="E14" s="25" t="n">
         <v>550000</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="33" t="n">
         <f aca="false">D14-E14</f>
         <v>130000</v>
       </c>
-      <c r="G14" s="29" t="n">
+      <c r="G14" s="33" t="n">
         <f aca="false">G13+F14</f>
         <v>-1786000</v>
       </c>
-      <c r="H14" s="43" t="n">
+      <c r="H14" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B14/単位経済性!$C$5)</f>
         <v>222.222222222222</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="42" t="s">
-        <v>159</v>
-      </c>
-      <c r="B15" s="21" t="n">
+      <c r="A15" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="B15" s="25" t="n">
         <v>4700000</v>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C15" s="19" t="n">
         <v>0.17</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="33" t="n">
         <f aca="false">B15*C15</f>
         <v>799000</v>
       </c>
-      <c r="E15" s="21" t="n">
+      <c r="E15" s="25" t="n">
         <v>550000</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="33" t="n">
         <f aca="false">D15-E15</f>
         <v>249000</v>
       </c>
-      <c r="G15" s="29" t="n">
+      <c r="G15" s="33" t="n">
         <f aca="false">G14+F15</f>
         <v>-1537000</v>
       </c>
-      <c r="H15" s="43" t="n">
+      <c r="H15" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B15/単位経済性!$C$5)</f>
         <v>261.111111111111</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="42" t="s">
-        <v>160</v>
-      </c>
-      <c r="B16" s="21" t="n">
+      <c r="A16" s="46" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" s="25" t="n">
         <v>5500000</v>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C16" s="19" t="n">
         <v>0.18</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="33" t="n">
         <f aca="false">B16*C16</f>
         <v>990000</v>
       </c>
-      <c r="E16" s="21" t="n">
+      <c r="E16" s="25" t="n">
         <v>550000</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="33" t="n">
         <f aca="false">D16-E16</f>
         <v>440000</v>
       </c>
-      <c r="G16" s="29" t="n">
+      <c r="G16" s="33" t="n">
         <f aca="false">G15+F16</f>
         <v>-1097000</v>
       </c>
-      <c r="H16" s="43" t="n">
+      <c r="H16" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B16/単位経済性!$C$5)</f>
         <v>305.555555555556</v>
       </c>
-      <c r="I16" s="17" t="s">
-        <v>161</v>
+      <c r="I16" s="21" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="44" t="s">
-        <v>162</v>
-      </c>
-      <c r="B17" s="45" t="n">
+      <c r="A17" s="48" t="s">
+        <v>166</v>
+      </c>
+      <c r="B17" s="49" t="n">
         <v>6000000</v>
       </c>
-      <c r="C17" s="46" t="n">
+      <c r="C17" s="50" t="n">
         <v>0.18</v>
       </c>
-      <c r="D17" s="47" t="n">
+      <c r="D17" s="51" t="n">
         <f aca="false">B17*C17</f>
         <v>1080000</v>
       </c>
-      <c r="E17" s="45" t="n">
+      <c r="E17" s="49" t="n">
         <v>700000</v>
       </c>
-      <c r="F17" s="47" t="n">
+      <c r="F17" s="51" t="n">
         <f aca="false">D17-E17</f>
         <v>380000</v>
       </c>
-      <c r="G17" s="47" t="n">
+      <c r="G17" s="51" t="n">
         <f aca="false">G16+F17</f>
         <v>-717000</v>
       </c>
-      <c r="H17" s="48" t="n">
+      <c r="H17" s="52" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B17/単位経済性!$C$5)</f>
         <v>333.333333333333</v>
       </c>
-      <c r="I17" s="17" t="s">
-        <v>163</v>
+      <c r="I17" s="21" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="42" t="s">
-        <v>164</v>
-      </c>
-      <c r="B18" s="21" t="n">
+      <c r="A18" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="B18" s="25" t="n">
         <v>7000000</v>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C18" s="19" t="n">
         <v>0.19</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="33" t="n">
         <f aca="false">B18*C18</f>
         <v>1330000</v>
       </c>
-      <c r="E18" s="21" t="n">
+      <c r="E18" s="25" t="n">
         <v>700000</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="33" t="n">
         <f aca="false">D18-E18</f>
         <v>630000</v>
       </c>
-      <c r="G18" s="29" t="n">
+      <c r="G18" s="33" t="n">
         <f aca="false">G17+F18</f>
         <v>-87000</v>
       </c>
-      <c r="H18" s="43" t="n">
+      <c r="H18" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B18/単位経済性!$C$5)</f>
         <v>388.888888888889</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="42" t="s">
-        <v>165</v>
-      </c>
-      <c r="B19" s="21" t="n">
+      <c r="A19" s="46" t="s">
+        <v>169</v>
+      </c>
+      <c r="B19" s="25" t="n">
         <v>8000000</v>
       </c>
-      <c r="C19" s="15" t="n">
+      <c r="C19" s="19" t="n">
         <v>0.19</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="33" t="n">
         <f aca="false">B19*C19</f>
         <v>1520000</v>
       </c>
-      <c r="E19" s="21" t="n">
+      <c r="E19" s="25" t="n">
         <v>700000</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="33" t="n">
         <f aca="false">D19-E19</f>
         <v>820000</v>
       </c>
-      <c r="G19" s="29" t="n">
+      <c r="G19" s="33" t="n">
         <f aca="false">G18+F19</f>
         <v>733000</v>
       </c>
-      <c r="H19" s="43" t="n">
+      <c r="H19" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B19/単位経済性!$C$5)</f>
         <v>444.444444444444</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="42" t="s">
-        <v>166</v>
-      </c>
-      <c r="B20" s="21" t="n">
+      <c r="A20" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="B20" s="25" t="n">
         <v>9000000</v>
       </c>
-      <c r="C20" s="15" t="n">
+      <c r="C20" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="33" t="n">
         <f aca="false">B20*C20</f>
         <v>1800000</v>
       </c>
-      <c r="E20" s="21" t="n">
+      <c r="E20" s="25" t="n">
         <v>900000</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="33" t="n">
         <f aca="false">D20-E20</f>
         <v>900000</v>
       </c>
-      <c r="G20" s="29" t="n">
+      <c r="G20" s="33" t="n">
         <f aca="false">G19+F20</f>
         <v>1633000</v>
       </c>
-      <c r="H20" s="43" t="n">
+      <c r="H20" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B20/単位経済性!$C$5)</f>
         <v>500</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="42" t="s">
-        <v>167</v>
-      </c>
-      <c r="B21" s="21" t="n">
+      <c r="A21" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="B21" s="25" t="n">
         <v>9500000</v>
       </c>
-      <c r="C21" s="15" t="n">
+      <c r="C21" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="33" t="n">
         <f aca="false">B21*C21</f>
         <v>1900000</v>
       </c>
-      <c r="E21" s="21" t="n">
+      <c r="E21" s="25" t="n">
         <v>900000</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="33" t="n">
         <f aca="false">D21-E21</f>
         <v>1000000</v>
       </c>
-      <c r="G21" s="29" t="n">
+      <c r="G21" s="33" t="n">
         <f aca="false">G20+F21</f>
         <v>2633000</v>
       </c>
-      <c r="H21" s="43" t="n">
+      <c r="H21" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B21/単位経済性!$C$5)</f>
         <v>527.777777777778</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="42" t="s">
-        <v>168</v>
-      </c>
-      <c r="B22" s="21" t="n">
+      <c r="A22" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="B22" s="25" t="n">
         <v>10000000</v>
       </c>
-      <c r="C22" s="15" t="n">
+      <c r="C22" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="33" t="n">
         <f aca="false">B22*C22</f>
         <v>2000000</v>
       </c>
-      <c r="E22" s="21" t="n">
+      <c r="E22" s="25" t="n">
         <v>900000</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="33" t="n">
         <f aca="false">D22-E22</f>
         <v>1100000</v>
       </c>
-      <c r="G22" s="29" t="n">
+      <c r="G22" s="33" t="n">
         <f aca="false">G21+F22</f>
         <v>3733000</v>
       </c>
-      <c r="H22" s="43" t="n">
+      <c r="H22" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B22/単位経済性!$C$5)</f>
         <v>555.555555555556</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="42" t="s">
-        <v>169</v>
-      </c>
-      <c r="B23" s="21" t="n">
+      <c r="A23" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="B23" s="25" t="n">
         <v>10500000</v>
       </c>
-      <c r="C23" s="15" t="n">
+      <c r="C23" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="33" t="n">
         <f aca="false">B23*C23</f>
         <v>2100000</v>
       </c>
-      <c r="E23" s="21" t="n">
+      <c r="E23" s="25" t="n">
         <v>1000000</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="33" t="n">
         <f aca="false">D23-E23</f>
         <v>1100000</v>
       </c>
-      <c r="G23" s="29" t="n">
+      <c r="G23" s="33" t="n">
         <f aca="false">G22+F23</f>
         <v>4833000</v>
       </c>
-      <c r="H23" s="43" t="n">
+      <c r="H23" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B23/単位経済性!$C$5)</f>
         <v>583.333333333333</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="42" t="s">
-        <v>170</v>
-      </c>
-      <c r="B24" s="21" t="n">
+      <c r="A24" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="B24" s="25" t="n">
         <v>10500000</v>
       </c>
-      <c r="C24" s="15" t="n">
+      <c r="C24" s="19" t="n">
         <v>0.21</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="33" t="n">
         <f aca="false">B24*C24</f>
         <v>2205000</v>
       </c>
-      <c r="E24" s="21" t="n">
+      <c r="E24" s="25" t="n">
         <v>1000000</v>
       </c>
-      <c r="F24" s="29" t="n">
+      <c r="F24" s="33" t="n">
         <f aca="false">D24-E24</f>
         <v>1205000</v>
       </c>
-      <c r="G24" s="29" t="n">
+      <c r="G24" s="33" t="n">
         <f aca="false">G23+F24</f>
         <v>6038000</v>
       </c>
-      <c r="H24" s="43" t="n">
+      <c r="H24" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B24/単位経済性!$C$5)</f>
         <v>583.333333333333</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="B25" s="21" t="n">
+      <c r="A25" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="B25" s="25" t="n">
         <v>11000000</v>
       </c>
-      <c r="C25" s="15" t="n">
+      <c r="C25" s="19" t="n">
         <v>0.21</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="33" t="n">
         <f aca="false">B25*C25</f>
         <v>2310000</v>
       </c>
-      <c r="E25" s="21" t="n">
+      <c r="E25" s="25" t="n">
         <v>1000000</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="33" t="n">
         <f aca="false">D25-E25</f>
         <v>1310000</v>
       </c>
-      <c r="G25" s="29" t="n">
+      <c r="G25" s="33" t="n">
         <f aca="false">G24+F25</f>
         <v>7348000</v>
       </c>
-      <c r="H25" s="43" t="n">
+      <c r="H25" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B25/単位経済性!$C$5)</f>
         <v>611.111111111111</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="42" t="s">
-        <v>172</v>
-      </c>
-      <c r="B26" s="21" t="n">
+      <c r="A26" s="46" t="s">
+        <v>176</v>
+      </c>
+      <c r="B26" s="25" t="n">
         <v>11500000</v>
       </c>
-      <c r="C26" s="15" t="n">
+      <c r="C26" s="19" t="n">
         <v>0.21</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="33" t="n">
         <f aca="false">B26*C26</f>
         <v>2415000</v>
       </c>
-      <c r="E26" s="21" t="n">
+      <c r="E26" s="25" t="n">
         <v>1100000</v>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="33" t="n">
         <f aca="false">D26-E26</f>
         <v>1315000</v>
       </c>
-      <c r="G26" s="29" t="n">
+      <c r="G26" s="33" t="n">
         <f aca="false">G25+F26</f>
         <v>8663000</v>
       </c>
-      <c r="H26" s="43" t="n">
+      <c r="H26" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B26/単位経済性!$C$5)</f>
         <v>638.888888888889</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="42" t="s">
-        <v>173</v>
-      </c>
-      <c r="B27" s="21" t="n">
+      <c r="A27" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="B27" s="25" t="n">
         <v>12000000</v>
       </c>
-      <c r="C27" s="15" t="n">
+      <c r="C27" s="19" t="n">
         <v>0.21</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="33" t="n">
         <f aca="false">B27*C27</f>
         <v>2520000</v>
       </c>
-      <c r="E27" s="21" t="n">
+      <c r="E27" s="25" t="n">
         <v>1100000</v>
       </c>
-      <c r="F27" s="29" t="n">
+      <c r="F27" s="33" t="n">
         <f aca="false">D27-E27</f>
         <v>1420000</v>
       </c>
-      <c r="G27" s="29" t="n">
+      <c r="G27" s="33" t="n">
         <f aca="false">G26+F27</f>
         <v>10083000</v>
       </c>
-      <c r="H27" s="43" t="n">
+      <c r="H27" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B27/単位経済性!$C$5)</f>
         <v>666.666666666667</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="42" t="s">
-        <v>174</v>
-      </c>
-      <c r="B28" s="21" t="n">
+      <c r="A28" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="B28" s="25" t="n">
         <v>12500000</v>
       </c>
-      <c r="C28" s="15" t="n">
+      <c r="C28" s="19" t="n">
         <v>0.22</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="33" t="n">
         <f aca="false">B28*C28</f>
         <v>2750000</v>
       </c>
-      <c r="E28" s="21" t="n">
+      <c r="E28" s="25" t="n">
         <v>1100000</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="33" t="n">
         <f aca="false">D28-E28</f>
         <v>1650000</v>
       </c>
-      <c r="G28" s="29" t="n">
+      <c r="G28" s="33" t="n">
         <f aca="false">G27+F28</f>
         <v>11733000</v>
       </c>
-      <c r="H28" s="43" t="n">
+      <c r="H28" s="47" t="n">
         <f aca="false">IF(単位経済性!$C$5=0,0,B28/単位経済性!$C$5)</f>
         <v>694.444444444445</v>
       </c>
-      <c r="I28" s="17" t="s">
-        <v>175</v>
+      <c r="I28" s="21" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="B30" s="22" t="n">
+      <c r="A30" s="46" t="s">
+        <v>180</v>
+      </c>
+      <c r="B30" s="26" t="n">
         <f aca="false">SUM(B5:B16)</f>
         <v>27700000</v>
       </c>
-      <c r="C30" s="32" t="n">
+      <c r="C30" s="36" t="n">
         <f aca="false">IF(B30=0,0,D30/B30)</f>
         <v>0.15985559566787</v>
       </c>
-      <c r="D30" s="22" t="n">
+      <c r="D30" s="26" t="n">
         <f aca="false">SUM(D5:D16)</f>
         <v>4428000</v>
       </c>
-      <c r="E30" s="22" t="n">
+      <c r="E30" s="26" t="n">
         <f aca="false">SUM(E5:E16)</f>
         <v>5525000</v>
       </c>
-      <c r="F30" s="22" t="n">
+      <c r="F30" s="26" t="n">
         <f aca="false">SUM(F5:F16)</f>
         <v>-1097000</v>
       </c>
-      <c r="H30" s="49" t="n">
+      <c r="H30" s="53" t="n">
         <f aca="false">SUM(H5:H16)</f>
         <v>1538.88888888889</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="42" t="s">
-        <v>177</v>
-      </c>
-      <c r="B31" s="22" t="n">
+      <c r="A31" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="B31" s="26" t="n">
         <f aca="false">SUM(B17:B28)</f>
         <v>117500000</v>
       </c>
-      <c r="C31" s="32" t="n">
+      <c r="C31" s="36" t="n">
         <f aca="false">IF(B31=0,0,D31/B31)</f>
         <v>0.203659574468085</v>
       </c>
-      <c r="D31" s="22" t="n">
+      <c r="D31" s="26" t="n">
         <f aca="false">SUM(D17:D28)</f>
         <v>23930000</v>
       </c>
-      <c r="E31" s="22" t="n">
+      <c r="E31" s="26" t="n">
         <f aca="false">SUM(E17:E28)</f>
         <v>11100000</v>
       </c>
-      <c r="F31" s="22" t="n">
+      <c r="F31" s="26" t="n">
         <f aca="false">SUM(F17:F28)</f>
         <v>12830000</v>
       </c>
-      <c r="H31" s="49" t="n">
+      <c r="H31" s="53" t="n">
         <f aca="false">SUM(H17:H28)</f>
         <v>6527.77777777778</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="50" t="s">
-        <v>179</v>
-      </c>
-      <c r="B34" s="29" t="n">
+      <c r="A34" s="54" t="s">
+        <v>183</v>
+      </c>
+      <c r="B34" s="33" t="n">
         <f aca="false">F30</f>
         <v>-1097000</v>
       </c>
@@ -4219,10 +5720,10 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="B35" s="38" t="n">
+      <c r="A35" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="B35" s="42" t="n">
         <f aca="false">前提!$B$40+F30</f>
         <v>-1097000</v>
       </c>
@@ -4232,10 +5733,10 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="B36" s="51" t="str">
+      <c r="A36" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="B36" s="55" t="str">
         <f aca="false">IFERROR(INDEX($A$5:$A$28,MATCH(TRUE(),INDEX($F$5:$F$28&gt;=0,0),0)),"—")</f>
         <v>M9</v>
       </c>
@@ -4256,6 +5757,954 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:J61"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="56" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="57" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="58" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="61" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="61" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="62" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C7" s="57" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="63" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C8" s="64" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B9" s="62" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C9" s="57" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="65" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" s="62" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C10" s="57" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="61" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11" s="62" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C11" s="57" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="61" t="s">
+        <v>201</v>
+      </c>
+      <c r="B12" s="62" t="n">
+        <v>88000</v>
+      </c>
+      <c r="C12" s="64"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="66" t="n">
+        <f aca="false">SUM(B6:B12)</f>
+        <v>600000</v>
+      </c>
+      <c r="C13" s="57" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="59" t="s">
+        <v>203</v>
+      </c>
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="61" t="s">
+        <v>204</v>
+      </c>
+      <c r="B16" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="57" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="61" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="57" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="61" t="s">
+        <v>207</v>
+      </c>
+      <c r="B18" s="62" t="n">
+        <v>12500</v>
+      </c>
+      <c r="C18" s="57" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="62" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C19" s="57" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="61" t="s">
+        <v>210</v>
+      </c>
+      <c r="B20" s="62" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C20" s="64" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="66" t="n">
+        <f aca="false">SUM(B16:B20)</f>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" s="60"/>
+      <c r="C23" s="60"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="61" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="67" t="n">
+        <f aca="false">単位経済性!$B$19</f>
+        <v>0.145833333333333</v>
+      </c>
+      <c r="C24" s="57" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="B25" s="68" t="n">
+        <f aca="false">IF(B24&lt;=0,"—",B21/B24)</f>
+        <v>137142.857142857</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" s="69" t="n">
+        <f aca="false">IF(OR(B24&lt;=0,単位経済性!$C$5=0),"—",B25/単位経済性!$C$5)</f>
+        <v>7.61904761904762</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="65" t="s">
+        <v>214</v>
+      </c>
+      <c r="B27" s="70" t="n">
+        <v>38</v>
+      </c>
+      <c r="C27" s="57" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="B28" s="71" t="n">
+        <f aca="false">IF(B26="—","—",B26*B27/60)</f>
+        <v>4.82539682539683</v>
+      </c>
+      <c r="C28" s="57" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="59" t="s">
+        <v>218</v>
+      </c>
+      <c r="B30" s="60"/>
+      <c r="C30" s="60"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="72" t="s">
+        <v>219</v>
+      </c>
+      <c r="B31" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="73" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D31" s="73" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E31" s="73" t="n">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="61" t="s">
+        <v>220</v>
+      </c>
+      <c r="B32" s="74" t="n">
+        <f aca="false">SUM($B$17:$B$20)+B$31</f>
+        <v>20000</v>
+      </c>
+      <c r="C32" s="74" t="n">
+        <f aca="false">SUM($B$17:$B$20)+C$31</f>
+        <v>120000</v>
+      </c>
+      <c r="D32" s="74" t="n">
+        <f aca="false">SUM($B$17:$B$20)+D$31</f>
+        <v>220000</v>
+      </c>
+      <c r="E32" s="74" t="n">
+        <f aca="false">SUM($B$17:$B$20)+E$31</f>
+        <v>320000</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="B33" s="75" t="n">
+        <f aca="false">IF($B$24&lt;=0,"—",B32/$B$24)</f>
+        <v>137142.857142857</v>
+      </c>
+      <c r="C33" s="75" t="n">
+        <f aca="false">IF($B$24&lt;=0,"—",C32/$B$24)</f>
+        <v>822857.142857143</v>
+      </c>
+      <c r="D33" s="75" t="n">
+        <f aca="false">IF($B$24&lt;=0,"—",D32/$B$24)</f>
+        <v>1508571.42857143</v>
+      </c>
+      <c r="E33" s="75" t="n">
+        <f aca="false">IF($B$24&lt;=0,"—",E32/$B$24)</f>
+        <v>2194285.71428571</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34" s="76" t="n">
+        <f aca="false">IF(OR($B$24&lt;=0,単位経済性!$C$5=0),"—",B33/単位経済性!$C$5)</f>
+        <v>7.61904761904762</v>
+      </c>
+      <c r="C34" s="76" t="n">
+        <f aca="false">IF(OR($B$24&lt;=0,単位経済性!$C$5=0),"—",C33/単位経済性!$C$5)</f>
+        <v>45.7142857142857</v>
+      </c>
+      <c r="D34" s="76" t="n">
+        <f aca="false">IF(OR($B$24&lt;=0,単位経済性!$C$5=0),"—",D33/単位経済性!$C$5)</f>
+        <v>83.8095238095238</v>
+      </c>
+      <c r="E34" s="76" t="n">
+        <f aca="false">IF(OR($B$24&lt;=0,単位経済性!$C$5=0),"—",E33/単位経済性!$C$5)</f>
+        <v>121.904761904762</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="61" t="s">
+        <v>216</v>
+      </c>
+      <c r="B35" s="77" t="n">
+        <f aca="false">IF(B34="—","—",B34*$B$27/60)</f>
+        <v>4.82539682539683</v>
+      </c>
+      <c r="C35" s="77" t="n">
+        <f aca="false">IF(C34="—","—",C34*$B$27/60)</f>
+        <v>28.952380952381</v>
+      </c>
+      <c r="D35" s="77" t="n">
+        <f aca="false">IF(D34="—","—",D34*$B$27/60)</f>
+        <v>53.0793650793651</v>
+      </c>
+      <c r="E35" s="77" t="n">
+        <f aca="false">IF(E34="—","—",E34*$B$27/60)</f>
+        <v>77.2063492063492</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="58" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="59" t="s">
+        <v>223</v>
+      </c>
+      <c r="B38" s="60"/>
+      <c r="C38" s="60"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="78" t="s">
+        <v>142</v>
+      </c>
+      <c r="B39" s="78" t="s">
+        <v>224</v>
+      </c>
+      <c r="C39" s="78" t="s">
+        <v>125</v>
+      </c>
+      <c r="D39" s="78" t="s">
+        <v>225</v>
+      </c>
+      <c r="E39" s="78" t="s">
+        <v>226</v>
+      </c>
+      <c r="F39" s="78" t="s">
+        <v>227</v>
+      </c>
+      <c r="G39" s="78" t="s">
+        <v>228</v>
+      </c>
+      <c r="H39" s="78" t="s">
+        <v>148</v>
+      </c>
+      <c r="I39" s="78" t="s">
+        <v>229</v>
+      </c>
+      <c r="J39" s="78" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="79" t="s">
+        <v>149</v>
+      </c>
+      <c r="B40" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="74" t="n">
+        <f aca="false">B40*C40</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="81" t="n">
+        <f aca="false">$B$21</f>
+        <v>20000</v>
+      </c>
+      <c r="F40" s="74" t="n">
+        <f aca="false">D40-E40</f>
+        <v>-20000</v>
+      </c>
+      <c r="G40" s="74" t="n">
+        <f aca="false">F40</f>
+        <v>-20000</v>
+      </c>
+      <c r="H40" s="76" t="n">
+        <f aca="false">IF(単位経済性!$C$5=0,0,B40/単位経済性!$C$5)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="77" t="n">
+        <f aca="false">H40*$B$27/60</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="57" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="79" t="s">
+        <v>151</v>
+      </c>
+      <c r="B41" s="62" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C41" s="80" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D41" s="74" t="n">
+        <f aca="false">B41*C41</f>
+        <v>8000</v>
+      </c>
+      <c r="E41" s="81" t="n">
+        <f aca="false">$B$21</f>
+        <v>20000</v>
+      </c>
+      <c r="F41" s="74" t="n">
+        <f aca="false">D41-E41</f>
+        <v>-12000</v>
+      </c>
+      <c r="G41" s="74" t="n">
+        <f aca="false">G40+F41</f>
+        <v>-32000</v>
+      </c>
+      <c r="H41" s="76" t="n">
+        <f aca="false">IF(単位経済性!$C$5=0,0,B41/単位経済性!$C$5)</f>
+        <v>5.55555555555556</v>
+      </c>
+      <c r="I41" s="77" t="n">
+        <f aca="false">H41*$B$27/60</f>
+        <v>3.51851851851852</v>
+      </c>
+      <c r="J41" s="57" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B42" s="62" t="n">
+        <v>200000</v>
+      </c>
+      <c r="C42" s="80" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D42" s="74" t="n">
+        <f aca="false">B42*C42</f>
+        <v>20000</v>
+      </c>
+      <c r="E42" s="81" t="n">
+        <f aca="false">$B$21</f>
+        <v>20000</v>
+      </c>
+      <c r="F42" s="74" t="n">
+        <f aca="false">D42-E42</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="74" t="n">
+        <f aca="false">G41+F42</f>
+        <v>-32000</v>
+      </c>
+      <c r="H42" s="76" t="n">
+        <f aca="false">IF(単位経済性!$C$5=0,0,B42/単位経済性!$C$5)</f>
+        <v>11.1111111111111</v>
+      </c>
+      <c r="I42" s="77" t="n">
+        <f aca="false">H42*$B$27/60</f>
+        <v>7.03703703703704</v>
+      </c>
+      <c r="J42" s="57" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="79" t="s">
+        <v>154</v>
+      </c>
+      <c r="B43" s="62" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C43" s="80" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D43" s="74" t="n">
+        <f aca="false">B43*C43</f>
+        <v>36000</v>
+      </c>
+      <c r="E43" s="81" t="n">
+        <f aca="false">$B$21</f>
+        <v>20000</v>
+      </c>
+      <c r="F43" s="74" t="n">
+        <f aca="false">D43-E43</f>
+        <v>16000</v>
+      </c>
+      <c r="G43" s="74" t="n">
+        <f aca="false">G42+F43</f>
+        <v>-16000</v>
+      </c>
+      <c r="H43" s="76" t="n">
+        <f aca="false">IF(単位経済性!$C$5=0,0,B43/単位経済性!$C$5)</f>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="I43" s="77" t="n">
+        <f aca="false">H43*$B$27/60</f>
+        <v>10.5555555555556</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="79" t="s">
+        <v>155</v>
+      </c>
+      <c r="B44" s="62" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C44" s="80" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D44" s="74" t="n">
+        <f aca="false">B44*C44</f>
+        <v>52000</v>
+      </c>
+      <c r="E44" s="81" t="n">
+        <f aca="false">$B$21</f>
+        <v>20000</v>
+      </c>
+      <c r="F44" s="74" t="n">
+        <f aca="false">D44-E44</f>
+        <v>32000</v>
+      </c>
+      <c r="G44" s="74" t="n">
+        <f aca="false">G43+F44</f>
+        <v>16000</v>
+      </c>
+      <c r="H44" s="76" t="n">
+        <f aca="false">IF(単位経済性!$C$5=0,0,B44/単位経済性!$C$5)</f>
+        <v>22.2222222222222</v>
+      </c>
+      <c r="I44" s="77" t="n">
+        <f aca="false">H44*$B$27/60</f>
+        <v>14.0740740740741</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="79" t="s">
+        <v>156</v>
+      </c>
+      <c r="B45" s="62" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C45" s="80" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D45" s="74" t="n">
+        <f aca="false">B45*C45</f>
+        <v>70000</v>
+      </c>
+      <c r="E45" s="81" t="n">
+        <f aca="false">$B$21</f>
+        <v>20000</v>
+      </c>
+      <c r="F45" s="74" t="n">
+        <f aca="false">D45-E45</f>
+        <v>50000</v>
+      </c>
+      <c r="G45" s="74" t="n">
+        <f aca="false">G44+F45</f>
+        <v>66000</v>
+      </c>
+      <c r="H45" s="76" t="n">
+        <f aca="false">IF(単位経済性!$C$5=0,0,B45/単位経済性!$C$5)</f>
+        <v>27.7777777777778</v>
+      </c>
+      <c r="I45" s="77" t="n">
+        <f aca="false">H45*$B$27/60</f>
+        <v>17.5925925925926</v>
+      </c>
+      <c r="J45" s="64" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="79" t="s">
+        <v>158</v>
+      </c>
+      <c r="B46" s="62" t="n">
+        <v>600000</v>
+      </c>
+      <c r="C46" s="80" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D46" s="74" t="n">
+        <f aca="false">B46*C46</f>
+        <v>90000</v>
+      </c>
+      <c r="E46" s="81" t="n">
+        <f aca="false">$B$21</f>
+        <v>20000</v>
+      </c>
+      <c r="F46" s="74" t="n">
+        <f aca="false">D46-E46</f>
+        <v>70000</v>
+      </c>
+      <c r="G46" s="74" t="n">
+        <f aca="false">G45+F46</f>
+        <v>136000</v>
+      </c>
+      <c r="H46" s="76" t="n">
+        <f aca="false">IF(単位経済性!$C$5=0,0,B46/単位経済性!$C$5)</f>
+        <v>33.3333333333333</v>
+      </c>
+      <c r="I46" s="77" t="n">
+        <f aca="false">H46*$B$27/60</f>
+        <v>21.1111111111111</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="79" t="s">
+        <v>159</v>
+      </c>
+      <c r="B47" s="62" t="n">
+        <v>700000</v>
+      </c>
+      <c r="C47" s="80" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D47" s="74" t="n">
+        <f aca="false">B47*C47</f>
+        <v>105000</v>
+      </c>
+      <c r="E47" s="81" t="n">
+        <f aca="false">$B$21</f>
+        <v>20000</v>
+      </c>
+      <c r="F47" s="74" t="n">
+        <f aca="false">D47-E47</f>
+        <v>85000</v>
+      </c>
+      <c r="G47" s="74" t="n">
+        <f aca="false">G46+F47</f>
+        <v>221000</v>
+      </c>
+      <c r="H47" s="76" t="n">
+        <f aca="false">IF(単位経済性!$C$5=0,0,B47/単位経済性!$C$5)</f>
+        <v>38.8888888888889</v>
+      </c>
+      <c r="I47" s="77" t="n">
+        <f aca="false">H47*$B$27/60</f>
+        <v>24.6296296296296</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="79" t="s">
+        <v>161</v>
+      </c>
+      <c r="B48" s="62" t="n">
+        <v>800000</v>
+      </c>
+      <c r="C48" s="80" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D48" s="74" t="n">
+        <f aca="false">B48*C48</f>
+        <v>128000</v>
+      </c>
+      <c r="E48" s="81" t="n">
+        <f aca="false">$B$21</f>
+        <v>20000</v>
+      </c>
+      <c r="F48" s="74" t="n">
+        <f aca="false">D48-E48</f>
+        <v>108000</v>
+      </c>
+      <c r="G48" s="74" t="n">
+        <f aca="false">G47+F48</f>
+        <v>329000</v>
+      </c>
+      <c r="H48" s="76" t="n">
+        <f aca="false">IF(単位経済性!$C$5=0,0,B48/単位経済性!$C$5)</f>
+        <v>44.4444444444444</v>
+      </c>
+      <c r="I48" s="77" t="n">
+        <f aca="false">H48*$B$27/60</f>
+        <v>28.1481481481482</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="79" t="s">
+        <v>162</v>
+      </c>
+      <c r="B49" s="62" t="n">
+        <v>900000</v>
+      </c>
+      <c r="C49" s="80" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D49" s="74" t="n">
+        <f aca="false">B49*C49</f>
+        <v>144000</v>
+      </c>
+      <c r="E49" s="81" t="n">
+        <f aca="false">$B$21</f>
+        <v>20000</v>
+      </c>
+      <c r="F49" s="74" t="n">
+        <f aca="false">D49-E49</f>
+        <v>124000</v>
+      </c>
+      <c r="G49" s="74" t="n">
+        <f aca="false">G48+F49</f>
+        <v>453000</v>
+      </c>
+      <c r="H49" s="76" t="n">
+        <f aca="false">IF(単位経済性!$C$5=0,0,B49/単位経済性!$C$5)</f>
+        <v>50</v>
+      </c>
+      <c r="I49" s="77" t="n">
+        <f aca="false">H49*$B$27/60</f>
+        <v>31.6666666666667</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="79" t="s">
+        <v>163</v>
+      </c>
+      <c r="B50" s="62" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C50" s="80" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D50" s="74" t="n">
+        <f aca="false">B50*C50</f>
+        <v>170000</v>
+      </c>
+      <c r="E50" s="81" t="n">
+        <f aca="false">$B$21</f>
+        <v>20000</v>
+      </c>
+      <c r="F50" s="74" t="n">
+        <f aca="false">D50-E50</f>
+        <v>150000</v>
+      </c>
+      <c r="G50" s="74" t="n">
+        <f aca="false">G49+F50</f>
+        <v>603000</v>
+      </c>
+      <c r="H50" s="76" t="n">
+        <f aca="false">IF(単位経済性!$C$5=0,0,B50/単位経済性!$C$5)</f>
+        <v>55.5555555555556</v>
+      </c>
+      <c r="I50" s="77" t="n">
+        <f aca="false">H50*$B$27/60</f>
+        <v>35.1851851851852</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="79" t="s">
+        <v>164</v>
+      </c>
+      <c r="B51" s="62" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="C51" s="80" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D51" s="74" t="n">
+        <f aca="false">B51*C51</f>
+        <v>216000</v>
+      </c>
+      <c r="E51" s="81" t="n">
+        <f aca="false">$B$21</f>
+        <v>20000</v>
+      </c>
+      <c r="F51" s="74" t="n">
+        <f aca="false">D51-E51</f>
+        <v>196000</v>
+      </c>
+      <c r="G51" s="74" t="n">
+        <f aca="false">G50+F51</f>
+        <v>799000</v>
+      </c>
+      <c r="H51" s="76" t="n">
+        <f aca="false">IF(単位経済性!$C$5=0,0,B51/単位経済性!$C$5)</f>
+        <v>66.6666666666667</v>
+      </c>
+      <c r="I51" s="77" t="n">
+        <f aca="false">H51*$B$27/60</f>
+        <v>42.2222222222222</v>
+      </c>
+      <c r="J51" s="64" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="79" t="s">
+        <v>180</v>
+      </c>
+      <c r="B52" s="66" t="n">
+        <f aca="false">SUM(B40:B51)</f>
+        <v>6700000</v>
+      </c>
+      <c r="C52" s="82" t="n">
+        <f aca="false">IF(B52=0,0,D52/B52)</f>
+        <v>0.155074626865672</v>
+      </c>
+      <c r="D52" s="66" t="n">
+        <f aca="false">SUM(D40:D51)</f>
+        <v>1039000</v>
+      </c>
+      <c r="E52" s="66" t="n">
+        <f aca="false">SUM(E40:E51)</f>
+        <v>240000</v>
+      </c>
+      <c r="F52" s="66" t="n">
+        <f aca="false">SUM(F40:F51)</f>
+        <v>799000</v>
+      </c>
+      <c r="H52" s="83" t="n">
+        <f aca="false">SUM(H40:H51)</f>
+        <v>372.222222222222</v>
+      </c>
+      <c r="I52" s="84" t="n">
+        <f aca="false">SUM(I40:I51)</f>
+        <v>235.740740740741</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="59" t="s">
+        <v>234</v>
+      </c>
+      <c r="B54" s="60"/>
+      <c r="C54" s="60"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="65" t="s">
+        <v>183</v>
+      </c>
+      <c r="B55" s="74" t="n">
+        <f aca="false">F52</f>
+        <v>799000</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B56" s="75" t="n">
+        <f aca="false">F52-B13</f>
+        <v>199000</v>
+      </c>
+      <c r="C56" s="14" t="str">
+        <f aca="false">IF(B56&gt;=0,"○ 初年度で初期投資を回収できる","✕ 未回収。回収に必要な追加額を確認")</f>
+        <v>○ 初年度で初期投資を回収できる</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="65" t="s">
+        <v>236</v>
+      </c>
+      <c r="B57" s="74" t="n">
+        <f aca="false">B51</f>
+        <v>1200000</v>
+      </c>
+      <c r="C57" s="14" t="str">
+        <f aca="false">IF(B57&gt;=1000000,"✅ 本格化：法人化・融資・FBA在庫化を検討",IF(B57&gt;=500000,"○ 継続：兼業のままもう1年規模を上げる","❌ 撤退検討：在庫を現金化して損失を確定する"))</f>
+        <v>✅ 本格化：法人化・融資・FBA在庫化を検討</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="61" t="s">
+        <v>237</v>
+      </c>
+      <c r="B58" s="74" t="n">
+        <f aca="false">-(B13-B8*0.6)</f>
+        <v>-360000</v>
+      </c>
+      <c r="C58" s="57" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="85" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="58" t="s">
+        <v>240</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:L22"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -4267,468 +6716,468 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>182</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>183</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="52" t="s">
-        <v>184</v>
+      <c r="A3" s="86" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="41" t="s">
-        <v>185</v>
-      </c>
-      <c r="B5" s="53" t="n">
+      <c r="A5" s="45" t="s">
+        <v>244</v>
+      </c>
+      <c r="B5" s="87" t="n">
         <v>0.05</v>
       </c>
-      <c r="C5" s="53" t="n">
+      <c r="C5" s="87" t="n">
         <v>0.075</v>
       </c>
-      <c r="D5" s="53" t="n">
+      <c r="D5" s="87" t="n">
         <v>0.1</v>
       </c>
-      <c r="E5" s="53" t="n">
+      <c r="E5" s="87" t="n">
         <v>0.125</v>
       </c>
-      <c r="F5" s="53" t="n">
+      <c r="F5" s="87" t="n">
         <v>0.15</v>
       </c>
-      <c r="G5" s="53" t="n">
+      <c r="G5" s="87" t="n">
         <v>0.175</v>
       </c>
-      <c r="H5" s="53" t="n">
+      <c r="H5" s="87" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="53" t="n">
+      <c r="A6" s="87" t="n">
         <v>0.25</v>
       </c>
-      <c r="B6" s="54" t="n">
+      <c r="B6" s="88" t="n">
         <f aca="false">1-$A6-B$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A6*前提!$B$6</f>
         <v>0.290833333333333</v>
       </c>
-      <c r="C6" s="54" t="n">
+      <c r="C6" s="88" t="n">
         <f aca="false">1-$A6-C$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A6*前提!$B$6</f>
         <v>0.265833333333333</v>
       </c>
-      <c r="D6" s="54" t="n">
+      <c r="D6" s="88" t="n">
         <f aca="false">1-$A6-D$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A6*前提!$B$6</f>
         <v>0.240833333333333</v>
       </c>
-      <c r="E6" s="54" t="n">
+      <c r="E6" s="88" t="n">
         <f aca="false">1-$A6-E$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A6*前提!$B$6</f>
         <v>0.215833333333333</v>
       </c>
-      <c r="F6" s="54" t="n">
+      <c r="F6" s="88" t="n">
         <f aca="false">1-$A6-F$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A6*前提!$B$6</f>
         <v>0.190833333333333</v>
       </c>
-      <c r="G6" s="54" t="n">
+      <c r="G6" s="88" t="n">
         <f aca="false">1-$A6-G$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A6*前提!$B$6</f>
         <v>0.165833333333333</v>
       </c>
-      <c r="H6" s="54" t="n">
+      <c r="H6" s="88" t="n">
         <f aca="false">1-$A6-H$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A6*前提!$B$6</f>
         <v>0.140833333333333</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>186</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="53" t="n">
+      <c r="A7" s="87" t="n">
         <v>0.275</v>
       </c>
-      <c r="B7" s="54" t="n">
+      <c r="B7" s="88" t="n">
         <f aca="false">1-$A7-B$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A7*前提!$B$6</f>
         <v>0.268333333333333</v>
       </c>
-      <c r="C7" s="54" t="n">
+      <c r="C7" s="88" t="n">
         <f aca="false">1-$A7-C$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A7*前提!$B$6</f>
         <v>0.243333333333333</v>
       </c>
-      <c r="D7" s="54" t="n">
+      <c r="D7" s="88" t="n">
         <f aca="false">1-$A7-D$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A7*前提!$B$6</f>
         <v>0.218333333333333</v>
       </c>
-      <c r="E7" s="54" t="n">
+      <c r="E7" s="88" t="n">
         <f aca="false">1-$A7-E$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A7*前提!$B$6</f>
         <v>0.193333333333333</v>
       </c>
-      <c r="F7" s="54" t="n">
+      <c r="F7" s="88" t="n">
         <f aca="false">1-$A7-F$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A7*前提!$B$6</f>
         <v>0.168333333333333</v>
       </c>
-      <c r="G7" s="54" t="n">
+      <c r="G7" s="88" t="n">
         <f aca="false">1-$A7-G$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A7*前提!$B$6</f>
         <v>0.143333333333333</v>
       </c>
-      <c r="H7" s="54" t="n">
+      <c r="H7" s="88" t="n">
         <f aca="false">1-$A7-H$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A7*前提!$B$6</f>
         <v>0.118333333333333</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>187</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="53" t="n">
+      <c r="A8" s="87" t="n">
         <v>0.3</v>
       </c>
-      <c r="B8" s="54" t="n">
+      <c r="B8" s="88" t="n">
         <f aca="false">1-$A8-B$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A8*前提!$B$6</f>
         <v>0.245833333333333</v>
       </c>
-      <c r="C8" s="54" t="n">
+      <c r="C8" s="88" t="n">
         <f aca="false">1-$A8-C$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A8*前提!$B$6</f>
         <v>0.220833333333333</v>
       </c>
-      <c r="D8" s="54" t="n">
+      <c r="D8" s="88" t="n">
         <f aca="false">1-$A8-D$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A8*前提!$B$6</f>
         <v>0.195833333333333</v>
       </c>
-      <c r="E8" s="54" t="n">
+      <c r="E8" s="88" t="n">
         <f aca="false">1-$A8-E$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A8*前提!$B$6</f>
         <v>0.170833333333333</v>
       </c>
-      <c r="F8" s="54" t="n">
+      <c r="F8" s="88" t="n">
         <f aca="false">1-$A8-F$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A8*前提!$B$6</f>
         <v>0.145833333333333</v>
       </c>
-      <c r="G8" s="54" t="n">
+      <c r="G8" s="88" t="n">
         <f aca="false">1-$A8-G$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A8*前提!$B$6</f>
         <v>0.120833333333333</v>
       </c>
-      <c r="H8" s="54" t="n">
+      <c r="H8" s="88" t="n">
         <f aca="false">1-$A8-H$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A8*前提!$B$6</f>
         <v>0.0958333333333333</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>188</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="53" t="n">
+      <c r="A9" s="87" t="n">
         <v>0.325</v>
       </c>
-      <c r="B9" s="54" t="n">
+      <c r="B9" s="88" t="n">
         <f aca="false">1-$A9-B$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A9*前提!$B$6</f>
         <v>0.223333333333333</v>
       </c>
-      <c r="C9" s="54" t="n">
+      <c r="C9" s="88" t="n">
         <f aca="false">1-$A9-C$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A9*前提!$B$6</f>
         <v>0.198333333333333</v>
       </c>
-      <c r="D9" s="54" t="n">
+      <c r="D9" s="88" t="n">
         <f aca="false">1-$A9-D$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A9*前提!$B$6</f>
         <v>0.173333333333333</v>
       </c>
-      <c r="E9" s="54" t="n">
+      <c r="E9" s="88" t="n">
         <f aca="false">1-$A9-E$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A9*前提!$B$6</f>
         <v>0.148333333333333</v>
       </c>
-      <c r="F9" s="54" t="n">
+      <c r="F9" s="88" t="n">
         <f aca="false">1-$A9-F$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A9*前提!$B$6</f>
         <v>0.123333333333333</v>
       </c>
-      <c r="G9" s="54" t="n">
+      <c r="G9" s="88" t="n">
         <f aca="false">1-$A9-G$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A9*前提!$B$6</f>
         <v>0.0983333333333333</v>
       </c>
-      <c r="H9" s="54" t="n">
+      <c r="H9" s="88" t="n">
         <f aca="false">1-$A9-H$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A9*前提!$B$6</f>
         <v>0.0733333333333334</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="53" t="n">
+      <c r="A10" s="87" t="n">
         <v>0.35</v>
       </c>
-      <c r="B10" s="54" t="n">
+      <c r="B10" s="88" t="n">
         <f aca="false">1-$A10-B$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A10*前提!$B$6</f>
         <v>0.200833333333333</v>
       </c>
-      <c r="C10" s="54" t="n">
+      <c r="C10" s="88" t="n">
         <f aca="false">1-$A10-C$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A10*前提!$B$6</f>
         <v>0.175833333333333</v>
       </c>
-      <c r="D10" s="54" t="n">
+      <c r="D10" s="88" t="n">
         <f aca="false">1-$A10-D$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A10*前提!$B$6</f>
         <v>0.150833333333333</v>
       </c>
-      <c r="E10" s="54" t="n">
+      <c r="E10" s="88" t="n">
         <f aca="false">1-$A10-E$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A10*前提!$B$6</f>
         <v>0.125833333333333</v>
       </c>
-      <c r="F10" s="54" t="n">
+      <c r="F10" s="88" t="n">
         <f aca="false">1-$A10-F$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A10*前提!$B$6</f>
         <v>0.100833333333333</v>
       </c>
-      <c r="G10" s="54" t="n">
+      <c r="G10" s="88" t="n">
         <f aca="false">1-$A10-G$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A10*前提!$B$6</f>
         <v>0.0758333333333334</v>
       </c>
-      <c r="H10" s="54" t="n">
+      <c r="H10" s="88" t="n">
         <f aca="false">1-$A10-H$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A10*前提!$B$6</f>
         <v>0.0508333333333334</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>189</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="53" t="n">
+      <c r="A11" s="87" t="n">
         <v>0.375</v>
       </c>
-      <c r="B11" s="54" t="n">
+      <c r="B11" s="88" t="n">
         <f aca="false">1-$A11-B$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A11*前提!$B$6</f>
         <v>0.178333333333333</v>
       </c>
-      <c r="C11" s="54" t="n">
+      <c r="C11" s="88" t="n">
         <f aca="false">1-$A11-C$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A11*前提!$B$6</f>
         <v>0.153333333333333</v>
       </c>
-      <c r="D11" s="54" t="n">
+      <c r="D11" s="88" t="n">
         <f aca="false">1-$A11-D$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A11*前提!$B$6</f>
         <v>0.128333333333333</v>
       </c>
-      <c r="E11" s="54" t="n">
+      <c r="E11" s="88" t="n">
         <f aca="false">1-$A11-E$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A11*前提!$B$6</f>
         <v>0.103333333333333</v>
       </c>
-      <c r="F11" s="54" t="n">
+      <c r="F11" s="88" t="n">
         <f aca="false">1-$A11-F$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A11*前提!$B$6</f>
         <v>0.0783333333333333</v>
       </c>
-      <c r="G11" s="54" t="n">
+      <c r="G11" s="88" t="n">
         <f aca="false">1-$A11-G$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A11*前提!$B$6</f>
         <v>0.0533333333333334</v>
       </c>
-      <c r="H11" s="54" t="n">
+      <c r="H11" s="88" t="n">
         <f aca="false">1-$A11-H$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A11*前提!$B$6</f>
         <v>0.0283333333333334</v>
       </c>
-      <c r="L11" s="36" t="s">
-        <v>190</v>
+      <c r="L11" s="40" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="53" t="n">
+      <c r="A12" s="87" t="n">
         <v>0.4</v>
       </c>
-      <c r="B12" s="54" t="n">
+      <c r="B12" s="88" t="n">
         <f aca="false">1-$A12-B$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A12*前提!$B$6</f>
         <v>0.155833333333333</v>
       </c>
-      <c r="C12" s="54" t="n">
+      <c r="C12" s="88" t="n">
         <f aca="false">1-$A12-C$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A12*前提!$B$6</f>
         <v>0.130833333333333</v>
       </c>
-      <c r="D12" s="54" t="n">
+      <c r="D12" s="88" t="n">
         <f aca="false">1-$A12-D$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A12*前提!$B$6</f>
         <v>0.105833333333333</v>
       </c>
-      <c r="E12" s="54" t="n">
+      <c r="E12" s="88" t="n">
         <f aca="false">1-$A12-E$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A12*前提!$B$6</f>
         <v>0.0808333333333333</v>
       </c>
-      <c r="F12" s="54" t="n">
+      <c r="F12" s="88" t="n">
         <f aca="false">1-$A12-F$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A12*前提!$B$6</f>
         <v>0.0558333333333333</v>
       </c>
-      <c r="G12" s="54" t="n">
+      <c r="G12" s="88" t="n">
         <f aca="false">1-$A12-G$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A12*前提!$B$6</f>
         <v>0.0308333333333334</v>
       </c>
-      <c r="H12" s="54" t="n">
+      <c r="H12" s="88" t="n">
         <f aca="false">1-$A12-H$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A12*前提!$B$6</f>
         <v>0.00583333333333331</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="53" t="n">
+      <c r="A13" s="87" t="n">
         <v>0.425</v>
       </c>
-      <c r="B13" s="54" t="n">
+      <c r="B13" s="88" t="n">
         <f aca="false">1-$A13-B$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A13*前提!$B$6</f>
         <v>0.133333333333333</v>
       </c>
-      <c r="C13" s="54" t="n">
+      <c r="C13" s="88" t="n">
         <f aca="false">1-$A13-C$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A13*前提!$B$6</f>
         <v>0.108333333333333</v>
       </c>
-      <c r="D13" s="54" t="n">
+      <c r="D13" s="88" t="n">
         <f aca="false">1-$A13-D$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A13*前提!$B$6</f>
         <v>0.0833333333333333</v>
       </c>
-      <c r="E13" s="54" t="n">
+      <c r="E13" s="88" t="n">
         <f aca="false">1-$A13-E$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A13*前提!$B$6</f>
         <v>0.0583333333333333</v>
       </c>
-      <c r="F13" s="54" t="n">
+      <c r="F13" s="88" t="n">
         <f aca="false">1-$A13-F$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A13*前提!$B$6</f>
         <v>0.0333333333333333</v>
       </c>
-      <c r="G13" s="54" t="n">
+      <c r="G13" s="88" t="n">
         <f aca="false">1-$A13-G$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A13*前提!$B$6</f>
         <v>0.0083333333333333</v>
       </c>
-      <c r="H13" s="54" t="n">
+      <c r="H13" s="88" t="n">
         <f aca="false">1-$A13-H$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A13*前提!$B$6</f>
         <v>-0.0166666666666667</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="53" t="n">
+      <c r="A14" s="87" t="n">
         <v>0.45</v>
       </c>
-      <c r="B14" s="54" t="n">
+      <c r="B14" s="88" t="n">
         <f aca="false">1-$A14-B$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A14*前提!$B$6</f>
         <v>0.110833333333333</v>
       </c>
-      <c r="C14" s="54" t="n">
+      <c r="C14" s="88" t="n">
         <f aca="false">1-$A14-C$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A14*前提!$B$6</f>
         <v>0.0858333333333334</v>
       </c>
-      <c r="D14" s="54" t="n">
+      <c r="D14" s="88" t="n">
         <f aca="false">1-$A14-D$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A14*前提!$B$6</f>
         <v>0.0608333333333334</v>
       </c>
-      <c r="E14" s="54" t="n">
+      <c r="E14" s="88" t="n">
         <f aca="false">1-$A14-E$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A14*前提!$B$6</f>
         <v>0.0358333333333334</v>
       </c>
-      <c r="F14" s="54" t="n">
+      <c r="F14" s="88" t="n">
         <f aca="false">1-$A14-F$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A14*前提!$B$6</f>
         <v>0.0108333333333333</v>
       </c>
-      <c r="G14" s="54" t="n">
+      <c r="G14" s="88" t="n">
         <f aca="false">1-$A14-G$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A14*前提!$B$6</f>
         <v>-0.0141666666666666</v>
       </c>
-      <c r="H14" s="54" t="n">
+      <c r="H14" s="88" t="n">
         <f aca="false">1-$A14-H$5-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+$A14*前提!$B$6</f>
         <v>-0.0391666666666666</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>191</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="55" t="s">
-        <v>192</v>
-      </c>
-      <c r="B18" s="56" t="n">
+      <c r="A18" s="89" t="s">
+        <v>251</v>
+      </c>
+      <c r="B18" s="90" t="n">
         <v>130</v>
       </c>
-      <c r="C18" s="56" t="n">
+      <c r="C18" s="90" t="n">
         <v>135</v>
       </c>
-      <c r="D18" s="56" t="n">
+      <c r="D18" s="90" t="n">
         <v>140</v>
       </c>
-      <c r="E18" s="56" t="n">
+      <c r="E18" s="90" t="n">
         <v>145</v>
       </c>
-      <c r="F18" s="56" t="n">
+      <c r="F18" s="90" t="n">
         <v>150</v>
       </c>
-      <c r="G18" s="56" t="n">
+      <c r="G18" s="90" t="n">
         <v>155</v>
       </c>
-      <c r="H18" s="56" t="n">
+      <c r="H18" s="90" t="n">
         <v>160</v>
       </c>
-      <c r="I18" s="56" t="n">
+      <c r="I18" s="90" t="n">
         <v>165</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="B19" s="54" t="n">
+      <c r="A19" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" s="88" t="n">
         <f aca="false">前提!$B$10/B$18/前提!$B$9</f>
         <v>0.384615384615385</v>
       </c>
-      <c r="C19" s="54" t="n">
+      <c r="C19" s="88" t="n">
         <f aca="false">前提!$B$10/C$18/前提!$B$9</f>
         <v>0.37037037037037</v>
       </c>
-      <c r="D19" s="54" t="n">
+      <c r="D19" s="88" t="n">
         <f aca="false">前提!$B$10/D$18/前提!$B$9</f>
         <v>0.357142857142857</v>
       </c>
-      <c r="E19" s="54" t="n">
+      <c r="E19" s="88" t="n">
         <f aca="false">前提!$B$10/E$18/前提!$B$9</f>
         <v>0.344827586206897</v>
       </c>
-      <c r="F19" s="54" t="n">
+      <c r="F19" s="88" t="n">
         <f aca="false">前提!$B$10/F$18/前提!$B$9</f>
         <v>0.333333333333333</v>
       </c>
-      <c r="G19" s="54" t="n">
+      <c r="G19" s="88" t="n">
         <f aca="false">前提!$B$10/G$18/前提!$B$9</f>
         <v>0.32258064516129</v>
       </c>
-      <c r="H19" s="54" t="n">
+      <c r="H19" s="88" t="n">
         <f aca="false">前提!$B$10/H$18/前提!$B$9</f>
         <v>0.3125</v>
       </c>
-      <c r="I19" s="54" t="n">
+      <c r="I19" s="88" t="n">
         <f aca="false">前提!$B$10/I$18/前提!$B$9</f>
         <v>0.303030303030303</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B20" s="57" t="n">
+        <v>125</v>
+      </c>
+      <c r="B20" s="91" t="n">
         <f aca="false">1-B19-前提!$B$13-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+B19*前提!$B$6</f>
         <v>0.0996794871794872</v>
       </c>
-      <c r="C20" s="57" t="n">
+      <c r="C20" s="91" t="n">
         <f aca="false">1-C19-前提!$B$13-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+C19*前提!$B$6</f>
         <v>0.1125</v>
       </c>
-      <c r="D20" s="57" t="n">
+      <c r="D20" s="91" t="n">
         <f aca="false">1-D19-前提!$B$13-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+D19*前提!$B$6</f>
         <v>0.124404761904762</v>
       </c>
-      <c r="E20" s="57" t="n">
+      <c r="E20" s="91" t="n">
         <f aca="false">1-E19-前提!$B$13-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+E19*前提!$B$6</f>
         <v>0.135488505747126</v>
       </c>
-      <c r="F20" s="57" t="n">
+      <c r="F20" s="91" t="n">
         <f aca="false">1-F19-前提!$B$13-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+F19*前提!$B$6</f>
         <v>0.145833333333333</v>
       </c>
-      <c r="G20" s="57" t="n">
+      <c r="G20" s="91" t="n">
         <f aca="false">1-G19-前提!$B$13-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+G19*前提!$B$6</f>
         <v>0.155510752688172</v>
       </c>
-      <c r="H20" s="57" t="n">
+      <c r="H20" s="91" t="n">
         <f aca="false">1-H19-前提!$B$13-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+H19*前提!$B$6</f>
         <v>0.164583333333333</v>
       </c>
-      <c r="I20" s="57" t="n">
+      <c r="I20" s="91" t="n">
         <f aca="false">1-I19-前提!$B$13-前提!$B$11-前提!$B$12/前提!$B$9-前提!$B$14/前提!$B$9-前提!$B$15-前提!$B$16-前提!$B$17+I19*前提!$B$6</f>
         <v>0.173106060606061</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="36" t="s">
-        <v>193</v>
+      <c r="A22" s="40" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -4766,7 +7215,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4795,997 +7244,997 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="36" t="s">
-        <v>195</v>
+      <c r="A2" s="40" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>196</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="B5" s="41" t="s">
-        <v>198</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>199</v>
-      </c>
-      <c r="D5" s="58" t="s">
-        <v>200</v>
-      </c>
-      <c r="E5" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="G5" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="H5" s="41" t="s">
-        <v>204</v>
-      </c>
-      <c r="I5" s="41" t="s">
-        <v>205</v>
-      </c>
-      <c r="J5" s="41" t="s">
-        <v>206</v>
-      </c>
-      <c r="K5" s="41" t="s">
-        <v>207</v>
-      </c>
-      <c r="L5" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="M5" s="41" t="s">
-        <v>209</v>
-      </c>
-      <c r="N5" s="41" t="s">
-        <v>210</v>
-      </c>
-      <c r="O5" s="41" t="s">
-        <v>211</v>
-      </c>
-      <c r="P5" s="41" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q5" s="41" t="s">
-        <v>213</v>
-      </c>
-      <c r="R5" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="S5" s="41" t="s">
-        <v>215</v>
-      </c>
-      <c r="T5" s="41" t="s">
-        <v>216</v>
-      </c>
-      <c r="U5" s="41" t="s">
-        <v>217</v>
-      </c>
-      <c r="V5" s="41" t="s">
-        <v>218</v>
+      <c r="A5" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>257</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>258</v>
+      </c>
+      <c r="D5" s="92" t="s">
+        <v>259</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>260</v>
+      </c>
+      <c r="F5" s="45" t="s">
+        <v>261</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="H5" s="45" t="s">
+        <v>263</v>
+      </c>
+      <c r="I5" s="45" t="s">
+        <v>264</v>
+      </c>
+      <c r="J5" s="45" t="s">
+        <v>265</v>
+      </c>
+      <c r="K5" s="45" t="s">
+        <v>266</v>
+      </c>
+      <c r="L5" s="45" t="s">
+        <v>267</v>
+      </c>
+      <c r="M5" s="45" t="s">
+        <v>268</v>
+      </c>
+      <c r="N5" s="45" t="s">
+        <v>269</v>
+      </c>
+      <c r="O5" s="45" t="s">
+        <v>270</v>
+      </c>
+      <c r="P5" s="45" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q5" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="R5" s="45" t="s">
+        <v>273</v>
+      </c>
+      <c r="S5" s="45" t="s">
+        <v>274</v>
+      </c>
+      <c r="T5" s="45" t="s">
+        <v>275</v>
+      </c>
+      <c r="U5" s="45" t="s">
+        <v>276</v>
+      </c>
+      <c r="V5" s="45" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="59" t="s">
-        <v>219</v>
-      </c>
-      <c r="B6" s="59" t="s">
-        <v>220</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>221</v>
-      </c>
-      <c r="D6" s="59" t="s">
-        <v>222</v>
-      </c>
-      <c r="E6" s="59" t="s">
-        <v>223</v>
-      </c>
-      <c r="F6" s="19" t="n">
+      <c r="A6" s="93" t="s">
+        <v>278</v>
+      </c>
+      <c r="B6" s="93" t="s">
+        <v>279</v>
+      </c>
+      <c r="C6" s="93" t="s">
+        <v>280</v>
+      </c>
+      <c r="D6" s="93" t="s">
+        <v>281</v>
+      </c>
+      <c r="E6" s="93" t="s">
+        <v>282</v>
+      </c>
+      <c r="F6" s="23" t="n">
         <v>320</v>
       </c>
-      <c r="G6" s="24" t="n">
+      <c r="G6" s="28" t="n">
         <v>150</v>
       </c>
-      <c r="H6" s="29" t="n">
+      <c r="H6" s="33" t="n">
         <f aca="false">F6*G6</f>
         <v>48000</v>
       </c>
-      <c r="I6" s="21" t="n">
+      <c r="I6" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="J6" s="29" t="n">
+      <c r="J6" s="33" t="n">
         <f aca="false">H6*前提!$B$11</f>
         <v>7200</v>
       </c>
-      <c r="K6" s="21" t="n">
+      <c r="K6" s="25" t="n">
         <v>2400</v>
       </c>
-      <c r="L6" s="21" t="n">
+      <c r="L6" s="25" t="n">
         <v>3200</v>
       </c>
-      <c r="M6" s="29" t="n">
+      <c r="M6" s="33" t="n">
         <f aca="false">H6*前提!$B$15</f>
         <v>4800</v>
       </c>
-      <c r="N6" s="60" t="s">
-        <v>224</v>
-      </c>
-      <c r="O6" s="59" t="s">
-        <v>225</v>
-      </c>
-      <c r="P6" s="59" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q6" s="59" t="s">
-        <v>227</v>
-      </c>
-      <c r="R6" s="59" t="s">
-        <v>228</v>
-      </c>
-      <c r="S6" s="59" t="s">
-        <v>229</v>
-      </c>
-      <c r="T6" s="29" t="n">
+      <c r="N6" s="94" t="s">
+        <v>283</v>
+      </c>
+      <c r="O6" s="93" t="s">
+        <v>284</v>
+      </c>
+      <c r="P6" s="93" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q6" s="93" t="s">
+        <v>286</v>
+      </c>
+      <c r="R6" s="93" t="s">
+        <v>287</v>
+      </c>
+      <c r="S6" s="93" t="s">
+        <v>288</v>
+      </c>
+      <c r="T6" s="33" t="n">
         <f aca="false">I6*前提!$B$6</f>
         <v>2000</v>
       </c>
-      <c r="U6" s="23" t="n">
+      <c r="U6" s="27" t="n">
         <f aca="false">H6-I6-J6-K6-L6-M6+T6</f>
         <v>12400</v>
       </c>
-      <c r="V6" s="61" t="n">
+      <c r="V6" s="95" t="n">
         <f aca="false">IF(H6=0,0,U6/H6)</f>
         <v>0.258333333333333</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="59"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="29" t="str">
+      <c r="A7" s="93"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="33" t="str">
         <f aca="false">IF(F7="","",F7*G7)</f>
         <v/>
       </c>
-      <c r="I7" s="59"/>
-      <c r="J7" s="29" t="str">
+      <c r="I7" s="93"/>
+      <c r="J7" s="33" t="str">
         <f aca="false">IF(H7="","",H7*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K7" s="59"/>
-      <c r="L7" s="59"/>
-      <c r="M7" s="29" t="str">
+      <c r="K7" s="93"/>
+      <c r="L7" s="93"/>
+      <c r="M7" s="33" t="str">
         <f aca="false">IF(H7="","",H7*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N7" s="59"/>
-      <c r="O7" s="59"/>
-      <c r="P7" s="59"/>
-      <c r="Q7" s="59"/>
-      <c r="R7" s="59"/>
-      <c r="S7" s="59"/>
-      <c r="T7" s="29" t="str">
+      <c r="N7" s="93"/>
+      <c r="O7" s="93"/>
+      <c r="P7" s="93"/>
+      <c r="Q7" s="93"/>
+      <c r="R7" s="93"/>
+      <c r="S7" s="93"/>
+      <c r="T7" s="33" t="str">
         <f aca="false">IF(I7="","",I7*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U7" s="29" t="str">
+      <c r="U7" s="33" t="str">
         <f aca="false">IF(H7="","",H7-N(I7)-N(J7)-N(K7)-N(L7)-N(M7)+N(T7))</f>
         <v/>
       </c>
-      <c r="V7" s="30" t="str">
+      <c r="V7" s="34" t="str">
         <f aca="false">IF(OR(H7="",H7=0),"",U7/H7)</f>
         <v/>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="59"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="29" t="str">
+      <c r="A8" s="93"/>
+      <c r="B8" s="93"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="33" t="str">
         <f aca="false">IF(F8="","",F8*G8)</f>
         <v/>
       </c>
-      <c r="I8" s="59"/>
-      <c r="J8" s="29" t="str">
+      <c r="I8" s="93"/>
+      <c r="J8" s="33" t="str">
         <f aca="false">IF(H8="","",H8*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K8" s="59"/>
-      <c r="L8" s="59"/>
-      <c r="M8" s="29" t="str">
+      <c r="K8" s="93"/>
+      <c r="L8" s="93"/>
+      <c r="M8" s="33" t="str">
         <f aca="false">IF(H8="","",H8*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N8" s="59"/>
-      <c r="O8" s="59"/>
-      <c r="P8" s="59"/>
-      <c r="Q8" s="59"/>
-      <c r="R8" s="59"/>
-      <c r="S8" s="59"/>
-      <c r="T8" s="29" t="str">
+      <c r="N8" s="93"/>
+      <c r="O8" s="93"/>
+      <c r="P8" s="93"/>
+      <c r="Q8" s="93"/>
+      <c r="R8" s="93"/>
+      <c r="S8" s="93"/>
+      <c r="T8" s="33" t="str">
         <f aca="false">IF(I8="","",I8*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U8" s="29" t="str">
+      <c r="U8" s="33" t="str">
         <f aca="false">IF(H8="","",H8-N(I8)-N(J8)-N(K8)-N(L8)-N(M8)+N(T8))</f>
         <v/>
       </c>
-      <c r="V8" s="30" t="str">
+      <c r="V8" s="34" t="str">
         <f aca="false">IF(OR(H8="",H8=0),"",U8/H8)</f>
         <v/>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="59"/>
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="29" t="str">
+      <c r="A9" s="93"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="33" t="str">
         <f aca="false">IF(F9="","",F9*G9)</f>
         <v/>
       </c>
-      <c r="I9" s="59"/>
-      <c r="J9" s="29" t="str">
+      <c r="I9" s="93"/>
+      <c r="J9" s="33" t="str">
         <f aca="false">IF(H9="","",H9*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K9" s="59"/>
-      <c r="L9" s="59"/>
-      <c r="M9" s="29" t="str">
+      <c r="K9" s="93"/>
+      <c r="L9" s="93"/>
+      <c r="M9" s="33" t="str">
         <f aca="false">IF(H9="","",H9*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N9" s="59"/>
-      <c r="O9" s="59"/>
-      <c r="P9" s="59"/>
-      <c r="Q9" s="59"/>
-      <c r="R9" s="59"/>
-      <c r="S9" s="59"/>
-      <c r="T9" s="29" t="str">
+      <c r="N9" s="93"/>
+      <c r="O9" s="93"/>
+      <c r="P9" s="93"/>
+      <c r="Q9" s="93"/>
+      <c r="R9" s="93"/>
+      <c r="S9" s="93"/>
+      <c r="T9" s="33" t="str">
         <f aca="false">IF(I9="","",I9*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U9" s="29" t="str">
+      <c r="U9" s="33" t="str">
         <f aca="false">IF(H9="","",H9-N(I9)-N(J9)-N(K9)-N(L9)-N(M9)+N(T9))</f>
         <v/>
       </c>
-      <c r="V9" s="30" t="str">
+      <c r="V9" s="34" t="str">
         <f aca="false">IF(OR(H9="",H9=0),"",U9/H9)</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="59"/>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="29" t="str">
+      <c r="A10" s="93"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="33" t="str">
         <f aca="false">IF(F10="","",F10*G10)</f>
         <v/>
       </c>
-      <c r="I10" s="59"/>
-      <c r="J10" s="29" t="str">
+      <c r="I10" s="93"/>
+      <c r="J10" s="33" t="str">
         <f aca="false">IF(H10="","",H10*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K10" s="59"/>
-      <c r="L10" s="59"/>
-      <c r="M10" s="29" t="str">
+      <c r="K10" s="93"/>
+      <c r="L10" s="93"/>
+      <c r="M10" s="33" t="str">
         <f aca="false">IF(H10="","",H10*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N10" s="59"/>
-      <c r="O10" s="59"/>
-      <c r="P10" s="59"/>
-      <c r="Q10" s="59"/>
-      <c r="R10" s="59"/>
-      <c r="S10" s="59"/>
-      <c r="T10" s="29" t="str">
+      <c r="N10" s="93"/>
+      <c r="O10" s="93"/>
+      <c r="P10" s="93"/>
+      <c r="Q10" s="93"/>
+      <c r="R10" s="93"/>
+      <c r="S10" s="93"/>
+      <c r="T10" s="33" t="str">
         <f aca="false">IF(I10="","",I10*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U10" s="29" t="str">
+      <c r="U10" s="33" t="str">
         <f aca="false">IF(H10="","",H10-N(I10)-N(J10)-N(K10)-N(L10)-N(M10)+N(T10))</f>
         <v/>
       </c>
-      <c r="V10" s="30" t="str">
+      <c r="V10" s="34" t="str">
         <f aca="false">IF(OR(H10="",H10=0),"",U10/H10)</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="59"/>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="29" t="str">
+      <c r="A11" s="93"/>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="33" t="str">
         <f aca="false">IF(F11="","",F11*G11)</f>
         <v/>
       </c>
-      <c r="I11" s="59"/>
-      <c r="J11" s="29" t="str">
+      <c r="I11" s="93"/>
+      <c r="J11" s="33" t="str">
         <f aca="false">IF(H11="","",H11*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K11" s="59"/>
-      <c r="L11" s="59"/>
-      <c r="M11" s="29" t="str">
+      <c r="K11" s="93"/>
+      <c r="L11" s="93"/>
+      <c r="M11" s="33" t="str">
         <f aca="false">IF(H11="","",H11*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N11" s="59"/>
-      <c r="O11" s="59"/>
-      <c r="P11" s="59"/>
-      <c r="Q11" s="59"/>
-      <c r="R11" s="59"/>
-      <c r="S11" s="59"/>
-      <c r="T11" s="29" t="str">
+      <c r="N11" s="93"/>
+      <c r="O11" s="93"/>
+      <c r="P11" s="93"/>
+      <c r="Q11" s="93"/>
+      <c r="R11" s="93"/>
+      <c r="S11" s="93"/>
+      <c r="T11" s="33" t="str">
         <f aca="false">IF(I11="","",I11*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U11" s="29" t="str">
+      <c r="U11" s="33" t="str">
         <f aca="false">IF(H11="","",H11-N(I11)-N(J11)-N(K11)-N(L11)-N(M11)+N(T11))</f>
         <v/>
       </c>
-      <c r="V11" s="30" t="str">
+      <c r="V11" s="34" t="str">
         <f aca="false">IF(OR(H11="",H11=0),"",U11/H11)</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="59"/>
-      <c r="B12" s="59"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="29" t="str">
+      <c r="A12" s="93"/>
+      <c r="B12" s="93"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="33" t="str">
         <f aca="false">IF(F12="","",F12*G12)</f>
         <v/>
       </c>
-      <c r="I12" s="59"/>
-      <c r="J12" s="29" t="str">
+      <c r="I12" s="93"/>
+      <c r="J12" s="33" t="str">
         <f aca="false">IF(H12="","",H12*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K12" s="59"/>
-      <c r="L12" s="59"/>
-      <c r="M12" s="29" t="str">
+      <c r="K12" s="93"/>
+      <c r="L12" s="93"/>
+      <c r="M12" s="33" t="str">
         <f aca="false">IF(H12="","",H12*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N12" s="59"/>
-      <c r="O12" s="59"/>
-      <c r="P12" s="59"/>
-      <c r="Q12" s="59"/>
-      <c r="R12" s="59"/>
-      <c r="S12" s="59"/>
-      <c r="T12" s="29" t="str">
+      <c r="N12" s="93"/>
+      <c r="O12" s="93"/>
+      <c r="P12" s="93"/>
+      <c r="Q12" s="93"/>
+      <c r="R12" s="93"/>
+      <c r="S12" s="93"/>
+      <c r="T12" s="33" t="str">
         <f aca="false">IF(I12="","",I12*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U12" s="29" t="str">
+      <c r="U12" s="33" t="str">
         <f aca="false">IF(H12="","",H12-N(I12)-N(J12)-N(K12)-N(L12)-N(M12)+N(T12))</f>
         <v/>
       </c>
-      <c r="V12" s="30" t="str">
+      <c r="V12" s="34" t="str">
         <f aca="false">IF(OR(H12="",H12=0),"",U12/H12)</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="59"/>
-      <c r="B13" s="59"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="29" t="str">
+      <c r="A13" s="93"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="33" t="str">
         <f aca="false">IF(F13="","",F13*G13)</f>
         <v/>
       </c>
-      <c r="I13" s="59"/>
-      <c r="J13" s="29" t="str">
+      <c r="I13" s="93"/>
+      <c r="J13" s="33" t="str">
         <f aca="false">IF(H13="","",H13*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K13" s="59"/>
-      <c r="L13" s="59"/>
-      <c r="M13" s="29" t="str">
+      <c r="K13" s="93"/>
+      <c r="L13" s="93"/>
+      <c r="M13" s="33" t="str">
         <f aca="false">IF(H13="","",H13*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N13" s="59"/>
-      <c r="O13" s="59"/>
-      <c r="P13" s="59"/>
-      <c r="Q13" s="59"/>
-      <c r="R13" s="59"/>
-      <c r="S13" s="59"/>
-      <c r="T13" s="29" t="str">
+      <c r="N13" s="93"/>
+      <c r="O13" s="93"/>
+      <c r="P13" s="93"/>
+      <c r="Q13" s="93"/>
+      <c r="R13" s="93"/>
+      <c r="S13" s="93"/>
+      <c r="T13" s="33" t="str">
         <f aca="false">IF(I13="","",I13*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U13" s="29" t="str">
+      <c r="U13" s="33" t="str">
         <f aca="false">IF(H13="","",H13-N(I13)-N(J13)-N(K13)-N(L13)-N(M13)+N(T13))</f>
         <v/>
       </c>
-      <c r="V13" s="30" t="str">
+      <c r="V13" s="34" t="str">
         <f aca="false">IF(OR(H13="",H13=0),"",U13/H13)</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="59"/>
-      <c r="B14" s="59"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="29" t="str">
+      <c r="A14" s="93"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="93"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="93"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="33" t="str">
         <f aca="false">IF(F14="","",F14*G14)</f>
         <v/>
       </c>
-      <c r="I14" s="59"/>
-      <c r="J14" s="29" t="str">
+      <c r="I14" s="93"/>
+      <c r="J14" s="33" t="str">
         <f aca="false">IF(H14="","",H14*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K14" s="59"/>
-      <c r="L14" s="59"/>
-      <c r="M14" s="29" t="str">
+      <c r="K14" s="93"/>
+      <c r="L14" s="93"/>
+      <c r="M14" s="33" t="str">
         <f aca="false">IF(H14="","",H14*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N14" s="59"/>
-      <c r="O14" s="59"/>
-      <c r="P14" s="59"/>
-      <c r="Q14" s="59"/>
-      <c r="R14" s="59"/>
-      <c r="S14" s="59"/>
-      <c r="T14" s="29" t="str">
+      <c r="N14" s="93"/>
+      <c r="O14" s="93"/>
+      <c r="P14" s="93"/>
+      <c r="Q14" s="93"/>
+      <c r="R14" s="93"/>
+      <c r="S14" s="93"/>
+      <c r="T14" s="33" t="str">
         <f aca="false">IF(I14="","",I14*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U14" s="29" t="str">
+      <c r="U14" s="33" t="str">
         <f aca="false">IF(H14="","",H14-N(I14)-N(J14)-N(K14)-N(L14)-N(M14)+N(T14))</f>
         <v/>
       </c>
-      <c r="V14" s="30" t="str">
+      <c r="V14" s="34" t="str">
         <f aca="false">IF(OR(H14="",H14=0),"",U14/H14)</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="59"/>
-      <c r="B15" s="59"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="29" t="str">
+      <c r="A15" s="93"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="93"/>
+      <c r="E15" s="93"/>
+      <c r="F15" s="93"/>
+      <c r="G15" s="93"/>
+      <c r="H15" s="33" t="str">
         <f aca="false">IF(F15="","",F15*G15)</f>
         <v/>
       </c>
-      <c r="I15" s="59"/>
-      <c r="J15" s="29" t="str">
+      <c r="I15" s="93"/>
+      <c r="J15" s="33" t="str">
         <f aca="false">IF(H15="","",H15*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K15" s="59"/>
-      <c r="L15" s="59"/>
-      <c r="M15" s="29" t="str">
+      <c r="K15" s="93"/>
+      <c r="L15" s="93"/>
+      <c r="M15" s="33" t="str">
         <f aca="false">IF(H15="","",H15*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N15" s="59"/>
-      <c r="O15" s="59"/>
-      <c r="P15" s="59"/>
-      <c r="Q15" s="59"/>
-      <c r="R15" s="59"/>
-      <c r="S15" s="59"/>
-      <c r="T15" s="29" t="str">
+      <c r="N15" s="93"/>
+      <c r="O15" s="93"/>
+      <c r="P15" s="93"/>
+      <c r="Q15" s="93"/>
+      <c r="R15" s="93"/>
+      <c r="S15" s="93"/>
+      <c r="T15" s="33" t="str">
         <f aca="false">IF(I15="","",I15*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U15" s="29" t="str">
+      <c r="U15" s="33" t="str">
         <f aca="false">IF(H15="","",H15-N(I15)-N(J15)-N(K15)-N(L15)-N(M15)+N(T15))</f>
         <v/>
       </c>
-      <c r="V15" s="30" t="str">
+      <c r="V15" s="34" t="str">
         <f aca="false">IF(OR(H15="",H15=0),"",U15/H15)</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="59"/>
-      <c r="B16" s="59"/>
-      <c r="C16" s="59"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="29" t="str">
+      <c r="A16" s="93"/>
+      <c r="B16" s="93"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="33" t="str">
         <f aca="false">IF(F16="","",F16*G16)</f>
         <v/>
       </c>
-      <c r="I16" s="59"/>
-      <c r="J16" s="29" t="str">
+      <c r="I16" s="93"/>
+      <c r="J16" s="33" t="str">
         <f aca="false">IF(H16="","",H16*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K16" s="59"/>
-      <c r="L16" s="59"/>
-      <c r="M16" s="29" t="str">
+      <c r="K16" s="93"/>
+      <c r="L16" s="93"/>
+      <c r="M16" s="33" t="str">
         <f aca="false">IF(H16="","",H16*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N16" s="59"/>
-      <c r="O16" s="59"/>
-      <c r="P16" s="59"/>
-      <c r="Q16" s="59"/>
-      <c r="R16" s="59"/>
-      <c r="S16" s="59"/>
-      <c r="T16" s="29" t="str">
+      <c r="N16" s="93"/>
+      <c r="O16" s="93"/>
+      <c r="P16" s="93"/>
+      <c r="Q16" s="93"/>
+      <c r="R16" s="93"/>
+      <c r="S16" s="93"/>
+      <c r="T16" s="33" t="str">
         <f aca="false">IF(I16="","",I16*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U16" s="29" t="str">
+      <c r="U16" s="33" t="str">
         <f aca="false">IF(H16="","",H16-N(I16)-N(J16)-N(K16)-N(L16)-N(M16)+N(T16))</f>
         <v/>
       </c>
-      <c r="V16" s="30" t="str">
+      <c r="V16" s="34" t="str">
         <f aca="false">IF(OR(H16="",H16=0),"",U16/H16)</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="59"/>
-      <c r="B17" s="59"/>
-      <c r="C17" s="59"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="29" t="str">
+      <c r="A17" s="93"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
+      <c r="F17" s="93"/>
+      <c r="G17" s="93"/>
+      <c r="H17" s="33" t="str">
         <f aca="false">IF(F17="","",F17*G17)</f>
         <v/>
       </c>
-      <c r="I17" s="59"/>
-      <c r="J17" s="29" t="str">
+      <c r="I17" s="93"/>
+      <c r="J17" s="33" t="str">
         <f aca="false">IF(H17="","",H17*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K17" s="59"/>
-      <c r="L17" s="59"/>
-      <c r="M17" s="29" t="str">
+      <c r="K17" s="93"/>
+      <c r="L17" s="93"/>
+      <c r="M17" s="33" t="str">
         <f aca="false">IF(H17="","",H17*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N17" s="59"/>
-      <c r="O17" s="59"/>
-      <c r="P17" s="59"/>
-      <c r="Q17" s="59"/>
-      <c r="R17" s="59"/>
-      <c r="S17" s="59"/>
-      <c r="T17" s="29" t="str">
+      <c r="N17" s="93"/>
+      <c r="O17" s="93"/>
+      <c r="P17" s="93"/>
+      <c r="Q17" s="93"/>
+      <c r="R17" s="93"/>
+      <c r="S17" s="93"/>
+      <c r="T17" s="33" t="str">
         <f aca="false">IF(I17="","",I17*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U17" s="29" t="str">
+      <c r="U17" s="33" t="str">
         <f aca="false">IF(H17="","",H17-N(I17)-N(J17)-N(K17)-N(L17)-N(M17)+N(T17))</f>
         <v/>
       </c>
-      <c r="V17" s="30" t="str">
+      <c r="V17" s="34" t="str">
         <f aca="false">IF(OR(H17="",H17=0),"",U17/H17)</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="59"/>
-      <c r="B18" s="59"/>
-      <c r="C18" s="59"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="59"/>
-      <c r="H18" s="29" t="str">
+      <c r="A18" s="93"/>
+      <c r="B18" s="93"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="93"/>
+      <c r="H18" s="33" t="str">
         <f aca="false">IF(F18="","",F18*G18)</f>
         <v/>
       </c>
-      <c r="I18" s="59"/>
-      <c r="J18" s="29" t="str">
+      <c r="I18" s="93"/>
+      <c r="J18" s="33" t="str">
         <f aca="false">IF(H18="","",H18*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K18" s="59"/>
-      <c r="L18" s="59"/>
-      <c r="M18" s="29" t="str">
+      <c r="K18" s="93"/>
+      <c r="L18" s="93"/>
+      <c r="M18" s="33" t="str">
         <f aca="false">IF(H18="","",H18*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N18" s="59"/>
-      <c r="O18" s="59"/>
-      <c r="P18" s="59"/>
-      <c r="Q18" s="59"/>
-      <c r="R18" s="59"/>
-      <c r="S18" s="59"/>
-      <c r="T18" s="29" t="str">
+      <c r="N18" s="93"/>
+      <c r="O18" s="93"/>
+      <c r="P18" s="93"/>
+      <c r="Q18" s="93"/>
+      <c r="R18" s="93"/>
+      <c r="S18" s="93"/>
+      <c r="T18" s="33" t="str">
         <f aca="false">IF(I18="","",I18*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U18" s="29" t="str">
+      <c r="U18" s="33" t="str">
         <f aca="false">IF(H18="","",H18-N(I18)-N(J18)-N(K18)-N(L18)-N(M18)+N(T18))</f>
         <v/>
       </c>
-      <c r="V18" s="30" t="str">
+      <c r="V18" s="34" t="str">
         <f aca="false">IF(OR(H18="",H18=0),"",U18/H18)</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="59"/>
-      <c r="B19" s="59"/>
-      <c r="C19" s="59"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="29" t="str">
+      <c r="A19" s="93"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="93"/>
+      <c r="H19" s="33" t="str">
         <f aca="false">IF(F19="","",F19*G19)</f>
         <v/>
       </c>
-      <c r="I19" s="59"/>
-      <c r="J19" s="29" t="str">
+      <c r="I19" s="93"/>
+      <c r="J19" s="33" t="str">
         <f aca="false">IF(H19="","",H19*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K19" s="59"/>
-      <c r="L19" s="59"/>
-      <c r="M19" s="29" t="str">
+      <c r="K19" s="93"/>
+      <c r="L19" s="93"/>
+      <c r="M19" s="33" t="str">
         <f aca="false">IF(H19="","",H19*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N19" s="59"/>
-      <c r="O19" s="59"/>
-      <c r="P19" s="59"/>
-      <c r="Q19" s="59"/>
-      <c r="R19" s="59"/>
-      <c r="S19" s="59"/>
-      <c r="T19" s="29" t="str">
+      <c r="N19" s="93"/>
+      <c r="O19" s="93"/>
+      <c r="P19" s="93"/>
+      <c r="Q19" s="93"/>
+      <c r="R19" s="93"/>
+      <c r="S19" s="93"/>
+      <c r="T19" s="33" t="str">
         <f aca="false">IF(I19="","",I19*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U19" s="29" t="str">
+      <c r="U19" s="33" t="str">
         <f aca="false">IF(H19="","",H19-N(I19)-N(J19)-N(K19)-N(L19)-N(M19)+N(T19))</f>
         <v/>
       </c>
-      <c r="V19" s="30" t="str">
+      <c r="V19" s="34" t="str">
         <f aca="false">IF(OR(H19="",H19=0),"",U19/H19)</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="59"/>
-      <c r="B20" s="59"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="29" t="str">
+      <c r="A20" s="93"/>
+      <c r="B20" s="93"/>
+      <c r="C20" s="93"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="33" t="str">
         <f aca="false">IF(F20="","",F20*G20)</f>
         <v/>
       </c>
-      <c r="I20" s="59"/>
-      <c r="J20" s="29" t="str">
+      <c r="I20" s="93"/>
+      <c r="J20" s="33" t="str">
         <f aca="false">IF(H20="","",H20*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K20" s="59"/>
-      <c r="L20" s="59"/>
-      <c r="M20" s="29" t="str">
+      <c r="K20" s="93"/>
+      <c r="L20" s="93"/>
+      <c r="M20" s="33" t="str">
         <f aca="false">IF(H20="","",H20*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N20" s="59"/>
-      <c r="O20" s="59"/>
-      <c r="P20" s="59"/>
-      <c r="Q20" s="59"/>
-      <c r="R20" s="59"/>
-      <c r="S20" s="59"/>
-      <c r="T20" s="29" t="str">
+      <c r="N20" s="93"/>
+      <c r="O20" s="93"/>
+      <c r="P20" s="93"/>
+      <c r="Q20" s="93"/>
+      <c r="R20" s="93"/>
+      <c r="S20" s="93"/>
+      <c r="T20" s="33" t="str">
         <f aca="false">IF(I20="","",I20*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U20" s="29" t="str">
+      <c r="U20" s="33" t="str">
         <f aca="false">IF(H20="","",H20-N(I20)-N(J20)-N(K20)-N(L20)-N(M20)+N(T20))</f>
         <v/>
       </c>
-      <c r="V20" s="30" t="str">
+      <c r="V20" s="34" t="str">
         <f aca="false">IF(OR(H20="",H20=0),"",U20/H20)</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="59"/>
-      <c r="B21" s="59"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="59"/>
-      <c r="H21" s="29" t="str">
+      <c r="A21" s="93"/>
+      <c r="B21" s="93"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="93"/>
+      <c r="E21" s="93"/>
+      <c r="F21" s="93"/>
+      <c r="G21" s="93"/>
+      <c r="H21" s="33" t="str">
         <f aca="false">IF(F21="","",F21*G21)</f>
         <v/>
       </c>
-      <c r="I21" s="59"/>
-      <c r="J21" s="29" t="str">
+      <c r="I21" s="93"/>
+      <c r="J21" s="33" t="str">
         <f aca="false">IF(H21="","",H21*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K21" s="59"/>
-      <c r="L21" s="59"/>
-      <c r="M21" s="29" t="str">
+      <c r="K21" s="93"/>
+      <c r="L21" s="93"/>
+      <c r="M21" s="33" t="str">
         <f aca="false">IF(H21="","",H21*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N21" s="59"/>
-      <c r="O21" s="59"/>
-      <c r="P21" s="59"/>
-      <c r="Q21" s="59"/>
-      <c r="R21" s="59"/>
-      <c r="S21" s="59"/>
-      <c r="T21" s="29" t="str">
+      <c r="N21" s="93"/>
+      <c r="O21" s="93"/>
+      <c r="P21" s="93"/>
+      <c r="Q21" s="93"/>
+      <c r="R21" s="93"/>
+      <c r="S21" s="93"/>
+      <c r="T21" s="33" t="str">
         <f aca="false">IF(I21="","",I21*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U21" s="29" t="str">
+      <c r="U21" s="33" t="str">
         <f aca="false">IF(H21="","",H21-N(I21)-N(J21)-N(K21)-N(L21)-N(M21)+N(T21))</f>
         <v/>
       </c>
-      <c r="V21" s="30" t="str">
+      <c r="V21" s="34" t="str">
         <f aca="false">IF(OR(H21="",H21=0),"",U21/H21)</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="59"/>
-      <c r="B22" s="59"/>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="29" t="str">
+      <c r="A22" s="93"/>
+      <c r="B22" s="93"/>
+      <c r="C22" s="93"/>
+      <c r="D22" s="93"/>
+      <c r="E22" s="93"/>
+      <c r="F22" s="93"/>
+      <c r="G22" s="93"/>
+      <c r="H22" s="33" t="str">
         <f aca="false">IF(F22="","",F22*G22)</f>
         <v/>
       </c>
-      <c r="I22" s="59"/>
-      <c r="J22" s="29" t="str">
+      <c r="I22" s="93"/>
+      <c r="J22" s="33" t="str">
         <f aca="false">IF(H22="","",H22*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K22" s="59"/>
-      <c r="L22" s="59"/>
-      <c r="M22" s="29" t="str">
+      <c r="K22" s="93"/>
+      <c r="L22" s="93"/>
+      <c r="M22" s="33" t="str">
         <f aca="false">IF(H22="","",H22*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N22" s="59"/>
-      <c r="O22" s="59"/>
-      <c r="P22" s="59"/>
-      <c r="Q22" s="59"/>
-      <c r="R22" s="59"/>
-      <c r="S22" s="59"/>
-      <c r="T22" s="29" t="str">
+      <c r="N22" s="93"/>
+      <c r="O22" s="93"/>
+      <c r="P22" s="93"/>
+      <c r="Q22" s="93"/>
+      <c r="R22" s="93"/>
+      <c r="S22" s="93"/>
+      <c r="T22" s="33" t="str">
         <f aca="false">IF(I22="","",I22*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U22" s="29" t="str">
+      <c r="U22" s="33" t="str">
         <f aca="false">IF(H22="","",H22-N(I22)-N(J22)-N(K22)-N(L22)-N(M22)+N(T22))</f>
         <v/>
       </c>
-      <c r="V22" s="30" t="str">
+      <c r="V22" s="34" t="str">
         <f aca="false">IF(OR(H22="",H22=0),"",U22/H22)</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="59"/>
-      <c r="B23" s="59"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="29" t="str">
+      <c r="A23" s="93"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="93"/>
+      <c r="D23" s="93"/>
+      <c r="E23" s="93"/>
+      <c r="F23" s="93"/>
+      <c r="G23" s="93"/>
+      <c r="H23" s="33" t="str">
         <f aca="false">IF(F23="","",F23*G23)</f>
         <v/>
       </c>
-      <c r="I23" s="59"/>
-      <c r="J23" s="29" t="str">
+      <c r="I23" s="93"/>
+      <c r="J23" s="33" t="str">
         <f aca="false">IF(H23="","",H23*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K23" s="59"/>
-      <c r="L23" s="59"/>
-      <c r="M23" s="29" t="str">
+      <c r="K23" s="93"/>
+      <c r="L23" s="93"/>
+      <c r="M23" s="33" t="str">
         <f aca="false">IF(H23="","",H23*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N23" s="59"/>
-      <c r="O23" s="59"/>
-      <c r="P23" s="59"/>
-      <c r="Q23" s="59"/>
-      <c r="R23" s="59"/>
-      <c r="S23" s="59"/>
-      <c r="T23" s="29" t="str">
+      <c r="N23" s="93"/>
+      <c r="O23" s="93"/>
+      <c r="P23" s="93"/>
+      <c r="Q23" s="93"/>
+      <c r="R23" s="93"/>
+      <c r="S23" s="93"/>
+      <c r="T23" s="33" t="str">
         <f aca="false">IF(I23="","",I23*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U23" s="29" t="str">
+      <c r="U23" s="33" t="str">
         <f aca="false">IF(H23="","",H23-N(I23)-N(J23)-N(K23)-N(L23)-N(M23)+N(T23))</f>
         <v/>
       </c>
-      <c r="V23" s="30" t="str">
+      <c r="V23" s="34" t="str">
         <f aca="false">IF(OR(H23="",H23=0),"",U23/H23)</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="59"/>
-      <c r="B24" s="59"/>
-      <c r="C24" s="59"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="29" t="str">
+      <c r="A24" s="93"/>
+      <c r="B24" s="93"/>
+      <c r="C24" s="93"/>
+      <c r="D24" s="93"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="93"/>
+      <c r="G24" s="93"/>
+      <c r="H24" s="33" t="str">
         <f aca="false">IF(F24="","",F24*G24)</f>
         <v/>
       </c>
-      <c r="I24" s="59"/>
-      <c r="J24" s="29" t="str">
+      <c r="I24" s="93"/>
+      <c r="J24" s="33" t="str">
         <f aca="false">IF(H24="","",H24*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K24" s="59"/>
-      <c r="L24" s="59"/>
-      <c r="M24" s="29" t="str">
+      <c r="K24" s="93"/>
+      <c r="L24" s="93"/>
+      <c r="M24" s="33" t="str">
         <f aca="false">IF(H24="","",H24*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N24" s="59"/>
-      <c r="O24" s="59"/>
-      <c r="P24" s="59"/>
-      <c r="Q24" s="59"/>
-      <c r="R24" s="59"/>
-      <c r="S24" s="59"/>
-      <c r="T24" s="29" t="str">
+      <c r="N24" s="93"/>
+      <c r="O24" s="93"/>
+      <c r="P24" s="93"/>
+      <c r="Q24" s="93"/>
+      <c r="R24" s="93"/>
+      <c r="S24" s="93"/>
+      <c r="T24" s="33" t="str">
         <f aca="false">IF(I24="","",I24*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U24" s="29" t="str">
+      <c r="U24" s="33" t="str">
         <f aca="false">IF(H24="","",H24-N(I24)-N(J24)-N(K24)-N(L24)-N(M24)+N(T24))</f>
         <v/>
       </c>
-      <c r="V24" s="30" t="str">
+      <c r="V24" s="34" t="str">
         <f aca="false">IF(OR(H24="",H24=0),"",U24/H24)</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="59"/>
-      <c r="B25" s="59"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="29" t="str">
+      <c r="A25" s="93"/>
+      <c r="B25" s="93"/>
+      <c r="C25" s="93"/>
+      <c r="D25" s="93"/>
+      <c r="E25" s="93"/>
+      <c r="F25" s="93"/>
+      <c r="G25" s="93"/>
+      <c r="H25" s="33" t="str">
         <f aca="false">IF(F25="","",F25*G25)</f>
         <v/>
       </c>
-      <c r="I25" s="59"/>
-      <c r="J25" s="29" t="str">
+      <c r="I25" s="93"/>
+      <c r="J25" s="33" t="str">
         <f aca="false">IF(H25="","",H25*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K25" s="59"/>
-      <c r="L25" s="59"/>
-      <c r="M25" s="29" t="str">
+      <c r="K25" s="93"/>
+      <c r="L25" s="93"/>
+      <c r="M25" s="33" t="str">
         <f aca="false">IF(H25="","",H25*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N25" s="59"/>
-      <c r="O25" s="59"/>
-      <c r="P25" s="59"/>
-      <c r="Q25" s="59"/>
-      <c r="R25" s="59"/>
-      <c r="S25" s="59"/>
-      <c r="T25" s="29" t="str">
+      <c r="N25" s="93"/>
+      <c r="O25" s="93"/>
+      <c r="P25" s="93"/>
+      <c r="Q25" s="93"/>
+      <c r="R25" s="93"/>
+      <c r="S25" s="93"/>
+      <c r="T25" s="33" t="str">
         <f aca="false">IF(I25="","",I25*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U25" s="29" t="str">
+      <c r="U25" s="33" t="str">
         <f aca="false">IF(H25="","",H25-N(I25)-N(J25)-N(K25)-N(L25)-N(M25)+N(T25))</f>
         <v/>
       </c>
-      <c r="V25" s="30" t="str">
+      <c r="V25" s="34" t="str">
         <f aca="false">IF(OR(H25="",H25=0),"",U25/H25)</f>
         <v/>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="59"/>
-      <c r="B26" s="59"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="29" t="str">
+      <c r="A26" s="93"/>
+      <c r="B26" s="93"/>
+      <c r="C26" s="93"/>
+      <c r="D26" s="93"/>
+      <c r="E26" s="93"/>
+      <c r="F26" s="93"/>
+      <c r="G26" s="93"/>
+      <c r="H26" s="33" t="str">
         <f aca="false">IF(F26="","",F26*G26)</f>
         <v/>
       </c>
-      <c r="I26" s="59"/>
-      <c r="J26" s="29" t="str">
+      <c r="I26" s="93"/>
+      <c r="J26" s="33" t="str">
         <f aca="false">IF(H26="","",H26*前提!$B$11)</f>
         <v/>
       </c>
-      <c r="K26" s="59"/>
-      <c r="L26" s="59"/>
-      <c r="M26" s="29" t="str">
+      <c r="K26" s="93"/>
+      <c r="L26" s="93"/>
+      <c r="M26" s="33" t="str">
         <f aca="false">IF(H26="","",H26*前提!$B$15)</f>
         <v/>
       </c>
-      <c r="N26" s="59"/>
-      <c r="O26" s="59"/>
-      <c r="P26" s="59"/>
-      <c r="Q26" s="59"/>
-      <c r="R26" s="59"/>
-      <c r="S26" s="59"/>
-      <c r="T26" s="29" t="str">
+      <c r="N26" s="93"/>
+      <c r="O26" s="93"/>
+      <c r="P26" s="93"/>
+      <c r="Q26" s="93"/>
+      <c r="R26" s="93"/>
+      <c r="S26" s="93"/>
+      <c r="T26" s="33" t="str">
         <f aca="false">IF(I26="","",I26*前提!$B$6)</f>
         <v/>
       </c>
-      <c r="U26" s="29" t="str">
+      <c r="U26" s="33" t="str">
         <f aca="false">IF(H26="","",H26-N(I26)-N(J26)-N(K26)-N(L26)-N(M26)+N(T26))</f>
         <v/>
       </c>
-      <c r="V26" s="30" t="str">
+      <c r="V26" s="34" t="str">
         <f aca="false">IF(OR(H26="",H26=0),"",U26/H26)</f>
         <v/>
       </c>
